--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_telecom_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1542283367934402</v>
+        <v>0.1538923887851359</v>
       </c>
       <c r="C2">
-        <v>936.5936450366839</v>
+        <v>931.8460958408549</v>
       </c>
       <c r="D2">
-        <v>904.5936450366839</v>
+        <v>907.4050958408549</v>
       </c>
       <c r="E2">
-        <v>-327.7</v>
+        <v>-320.141</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.559</v>
       </c>
       <c r="G2">
         <v>32</v>
@@ -1439,28 +1439,28 @@
         <v>104.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3802177</v>
       </c>
       <c r="N2">
-        <v>104.4</v>
+        <v>104.0197823</v>
       </c>
       <c r="O2">
-        <v>25.056</v>
+        <v>24.964747752</v>
       </c>
       <c r="P2">
-        <v>79.34400000000001</v>
+        <v>79.05503454800001</v>
       </c>
       <c r="Q2">
-        <v>164.944</v>
+        <v>164.655034548</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1542283367934402</v>
+        <v>0.1550607159445818</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5368385626540588</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>274.5795369337093</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1538923887851359</v>
+        <v>0.1535564407768317</v>
       </c>
       <c r="C3">
-        <v>931.8460958408549</v>
+        <v>927.1160769437498</v>
       </c>
       <c r="D3">
-        <v>907.4050958408549</v>
+        <v>910.2340769437499</v>
       </c>
       <c r="E3">
-        <v>-320.141</v>
+        <v>-312.582</v>
       </c>
       <c r="F3">
-        <v>7.559</v>
+        <v>15.118</v>
       </c>
       <c r="G3">
         <v>32</v>
@@ -1521,28 +1521,28 @@
         <v>104.4</v>
       </c>
       <c r="M3">
-        <v>0.3802177</v>
+        <v>0.7604354</v>
       </c>
       <c r="N3">
-        <v>104.0197823</v>
+        <v>103.6395646</v>
       </c>
       <c r="O3">
-        <v>24.964747752</v>
+        <v>24.873495504</v>
       </c>
       <c r="P3">
-        <v>79.05503454800001</v>
+        <v>78.766069096</v>
       </c>
       <c r="Q3">
-        <v>164.655034548</v>
+        <v>164.366069096</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1550607159445818</v>
+        <v>0.1559100824253384</v>
       </c>
       <c r="T3">
-        <v>0.5368385626540588</v>
+        <v>0.5410118162956259</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>274.5795369337093</v>
+        <v>137.2897684668546</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1535564407768317</v>
+        <v>0.1532204927685274</v>
       </c>
       <c r="C4">
-        <v>927.1160769437498</v>
+        <v>922.4037528187046</v>
       </c>
       <c r="D4">
-        <v>910.2340769437499</v>
+        <v>913.0807528187046</v>
       </c>
       <c r="E4">
-        <v>-312.582</v>
+        <v>-305.023</v>
       </c>
       <c r="F4">
-        <v>15.118</v>
+        <v>22.677</v>
       </c>
       <c r="G4">
         <v>32</v>
@@ -1603,28 +1603,28 @@
         <v>104.4</v>
       </c>
       <c r="M4">
-        <v>0.7604354</v>
+        <v>1.1406531</v>
       </c>
       <c r="N4">
-        <v>103.6395646</v>
+        <v>103.2593469</v>
       </c>
       <c r="O4">
-        <v>24.873495504</v>
+        <v>24.782243256</v>
       </c>
       <c r="P4">
-        <v>78.766069096</v>
+        <v>78.47710364400001</v>
       </c>
       <c r="Q4">
-        <v>164.366069096</v>
+        <v>164.077103644</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1559100824253384</v>
+        <v>0.1567769616170386</v>
       </c>
       <c r="T4">
-        <v>0.5410118162956259</v>
+        <v>0.5452711164040296</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>137.2897684668546</v>
+        <v>91.52651231123644</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1532204927685274</v>
+        <v>0.1528845447602231</v>
       </c>
       <c r="C5">
-        <v>922.4037528187046</v>
+        <v>917.7092900030132</v>
       </c>
       <c r="D5">
-        <v>913.0807528187046</v>
+        <v>915.9452900030132</v>
       </c>
       <c r="E5">
-        <v>-305.023</v>
+        <v>-297.464</v>
       </c>
       <c r="F5">
-        <v>22.677</v>
+        <v>30.236</v>
       </c>
       <c r="G5">
         <v>32</v>
@@ -1685,28 +1685,28 @@
         <v>104.4</v>
       </c>
       <c r="M5">
-        <v>1.1406531</v>
+        <v>1.5208708</v>
       </c>
       <c r="N5">
-        <v>103.2593469</v>
+        <v>102.8791292</v>
       </c>
       <c r="O5">
-        <v>24.782243256</v>
+        <v>24.690991008</v>
       </c>
       <c r="P5">
-        <v>78.47710364400001</v>
+        <v>78.18813819200001</v>
       </c>
       <c r="Q5">
-        <v>164.077103644</v>
+        <v>163.788138192</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1567769616170386</v>
+        <v>0.1576619007918991</v>
       </c>
       <c r="T5">
-        <v>0.5452711164040296</v>
+        <v>0.5496191519313582</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>91.52651231123644</v>
+        <v>68.64488423342733</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1528845447602231</v>
+        <v>0.1525485967519189</v>
       </c>
       <c r="C6">
-        <v>917.7092900030132</v>
+        <v>913.0328571304041</v>
       </c>
       <c r="D6">
-        <v>915.9452900030132</v>
+        <v>918.827857130404</v>
       </c>
       <c r="E6">
-        <v>-297.464</v>
+        <v>-289.905</v>
       </c>
       <c r="F6">
-        <v>30.236</v>
+        <v>37.795</v>
       </c>
       <c r="G6">
         <v>32</v>
@@ -1767,28 +1767,28 @@
         <v>104.4</v>
       </c>
       <c r="M6">
-        <v>1.5208708</v>
+        <v>1.9010885</v>
       </c>
       <c r="N6">
-        <v>102.8791292</v>
+        <v>102.4989115</v>
       </c>
       <c r="O6">
-        <v>24.690991008</v>
+        <v>24.59973876</v>
       </c>
       <c r="P6">
-        <v>78.18813819200001</v>
+        <v>77.89917274000001</v>
       </c>
       <c r="Q6">
-        <v>163.788138192</v>
+        <v>163.49917274</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1576619007918991</v>
+        <v>0.1585654702651778</v>
       </c>
       <c r="T6">
-        <v>0.5496191519313582</v>
+        <v>0.5540587250487359</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>68.64488423342733</v>
+        <v>54.91590738674186</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1525485967519189</v>
+        <v>0.1522126487436146</v>
       </c>
       <c r="C7">
-        <v>913.0328571304041</v>
+        <v>908.3746249641332</v>
       </c>
       <c r="D7">
-        <v>918.827857130404</v>
+        <v>921.7286249641332</v>
       </c>
       <c r="E7">
-        <v>-289.905</v>
+        <v>-282.346</v>
       </c>
       <c r="F7">
-        <v>37.795</v>
+        <v>45.354</v>
       </c>
       <c r="G7">
         <v>32</v>
@@ -1849,28 +1849,28 @@
         <v>104.4</v>
       </c>
       <c r="M7">
-        <v>1.9010885</v>
+        <v>2.2813062</v>
       </c>
       <c r="N7">
-        <v>102.4989115</v>
+        <v>102.1186938</v>
       </c>
       <c r="O7">
-        <v>24.59973876</v>
+        <v>24.508486512</v>
       </c>
       <c r="P7">
-        <v>77.89917274000001</v>
+        <v>77.610207288</v>
       </c>
       <c r="Q7">
-        <v>163.49917274</v>
+        <v>163.210207288</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1585654702651778</v>
+        <v>0.1594882646208667</v>
       </c>
       <c r="T7">
-        <v>0.5540587250487359</v>
+        <v>0.558592757168611</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>54.91590738674186</v>
+        <v>45.76325615561822</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1522126487436146</v>
+        <v>0.1518767007353104</v>
       </c>
       <c r="C8">
-        <v>908.3746249641332</v>
+        <v>903.7347664307067</v>
       </c>
       <c r="D8">
-        <v>921.7286249641332</v>
+        <v>924.6477664307067</v>
       </c>
       <c r="E8">
-        <v>-282.346</v>
+        <v>-274.787</v>
       </c>
       <c r="F8">
-        <v>45.354</v>
+        <v>52.91299999999999</v>
       </c>
       <c r="G8">
         <v>32</v>
@@ -1931,28 +1931,28 @@
         <v>104.4</v>
       </c>
       <c r="M8">
-        <v>2.2813062</v>
+        <v>2.661523899999999</v>
       </c>
       <c r="N8">
-        <v>102.1186938</v>
+        <v>101.7384761</v>
       </c>
       <c r="O8">
-        <v>24.508486512</v>
+        <v>24.417234264</v>
       </c>
       <c r="P8">
-        <v>77.610207288</v>
+        <v>77.321241836</v>
       </c>
       <c r="Q8">
-        <v>163.210207288</v>
+        <v>162.921241836</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1594882646208667</v>
+        <v>0.1604309040164628</v>
       </c>
       <c r="T8">
-        <v>0.558592757168611</v>
+        <v>0.5632242953555801</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>45.76325615561822</v>
+        <v>39.22564813338705</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1518767007353104</v>
+        <v>0.1515407527270061</v>
       </c>
       <c r="C9">
-        <v>903.7347664307067</v>
+        <v>899.1134566542421</v>
       </c>
       <c r="D9">
-        <v>924.6477664307067</v>
+        <v>927.5854566542421</v>
       </c>
       <c r="E9">
-        <v>-274.787</v>
+        <v>-267.228</v>
       </c>
       <c r="F9">
-        <v>52.913</v>
+        <v>60.472</v>
       </c>
       <c r="G9">
         <v>32</v>
@@ -2013,28 +2013,28 @@
         <v>104.4</v>
       </c>
       <c r="M9">
-        <v>2.6615239</v>
+        <v>3.0417416</v>
       </c>
       <c r="N9">
-        <v>101.7384761</v>
+        <v>101.3582584</v>
       </c>
       <c r="O9">
-        <v>24.417234264</v>
+        <v>24.325982016</v>
       </c>
       <c r="P9">
-        <v>77.321241836</v>
+        <v>77.03227638400001</v>
       </c>
       <c r="Q9">
-        <v>162.921241836</v>
+        <v>162.632276384</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1604309040164628</v>
+        <v>0.1613940355728327</v>
       </c>
       <c r="T9">
-        <v>0.5632242953555801</v>
+        <v>0.5679565191553094</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.22564813338704</v>
+        <v>34.32244211671367</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1515407527270061</v>
+        <v>0.1512048047187019</v>
       </c>
       <c r="C10">
-        <v>899.1134566542421</v>
+        <v>894.5108729914915</v>
       </c>
       <c r="D10">
-        <v>927.5854566542421</v>
+        <v>930.5418729914915</v>
       </c>
       <c r="E10">
-        <v>-267.228</v>
+        <v>-259.669</v>
       </c>
       <c r="F10">
-        <v>60.472</v>
+        <v>68.03099999999999</v>
       </c>
       <c r="G10">
         <v>32</v>
@@ -2095,28 +2095,28 @@
         <v>104.4</v>
       </c>
       <c r="M10">
-        <v>3.0417416</v>
+        <v>3.421959299999999</v>
       </c>
       <c r="N10">
-        <v>101.3582584</v>
+        <v>100.9780407</v>
       </c>
       <c r="O10">
-        <v>24.325982016</v>
+        <v>24.234729768</v>
       </c>
       <c r="P10">
-        <v>77.03227638400001</v>
+        <v>76.74331093200001</v>
       </c>
       <c r="Q10">
-        <v>162.632276384</v>
+        <v>162.343310932</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1613940355728327</v>
+        <v>0.1623783348557163</v>
       </c>
       <c r="T10">
-        <v>0.5679565191553094</v>
+        <v>0.5727927478737143</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.32244211671367</v>
+        <v>30.50883743707882</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1512048047187019</v>
+        <v>0.1508688567103976</v>
       </c>
       <c r="C11">
-        <v>894.5108729914915</v>
+        <v>889.9271950675358</v>
       </c>
       <c r="D11">
-        <v>930.5418729914915</v>
+        <v>933.5171950675358</v>
       </c>
       <c r="E11">
-        <v>-259.669</v>
+        <v>-252.11</v>
       </c>
       <c r="F11">
-        <v>68.03099999999999</v>
+        <v>75.58999999999999</v>
       </c>
       <c r="G11">
         <v>32</v>
@@ -2177,28 +2177,28 @@
         <v>104.4</v>
       </c>
       <c r="M11">
-        <v>3.421959299999999</v>
+        <v>3.802176999999999</v>
       </c>
       <c r="N11">
-        <v>100.9780407</v>
+        <v>100.597823</v>
       </c>
       <c r="O11">
-        <v>24.234729768</v>
+        <v>24.14347752</v>
       </c>
       <c r="P11">
-        <v>76.74331093200001</v>
+        <v>76.45434548</v>
       </c>
       <c r="Q11">
-        <v>162.343310932</v>
+        <v>162.05434548</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1623783348557163</v>
+        <v>0.1633845074559974</v>
       </c>
       <c r="T11">
-        <v>0.5727927478737143</v>
+        <v>0.5777364483414169</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.50883743707882</v>
+        <v>27.45795369337094</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1508688567103976</v>
+        <v>0.1505329087020933</v>
       </c>
       <c r="C12">
-        <v>889.9271950675358</v>
+        <v>885.3626048121635</v>
       </c>
       <c r="D12">
-        <v>933.5171950675358</v>
+        <v>936.5116048121635</v>
       </c>
       <c r="E12">
-        <v>-252.11</v>
+        <v>-244.551</v>
       </c>
       <c r="F12">
-        <v>75.59</v>
+        <v>83.149</v>
       </c>
       <c r="G12">
         <v>32</v>
@@ -2259,28 +2259,28 @@
         <v>104.4</v>
       </c>
       <c r="M12">
-        <v>3.802177</v>
+        <v>4.1823947</v>
       </c>
       <c r="N12">
-        <v>100.597823</v>
+        <v>100.2176053</v>
       </c>
       <c r="O12">
-        <v>24.14347752</v>
+        <v>24.052225272</v>
       </c>
       <c r="P12">
-        <v>76.45434548</v>
+        <v>76.165380028</v>
       </c>
       <c r="Q12">
-        <v>162.05434548</v>
+        <v>161.765380028</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1633845074559974</v>
+        <v>0.1644132906765094</v>
       </c>
       <c r="T12">
-        <v>0.5777364483414169</v>
+        <v>0.5827912432016522</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.45795369337093</v>
+        <v>24.96177608488266</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1505329087020933</v>
+        <v>0.1501969606937891</v>
       </c>
       <c r="C13">
-        <v>885.3626048121635</v>
+        <v>880.817286496952</v>
       </c>
       <c r="D13">
-        <v>936.5116048121635</v>
+        <v>939.5252864969519</v>
       </c>
       <c r="E13">
-        <v>-244.551</v>
+        <v>-236.992</v>
       </c>
       <c r="F13">
-        <v>83.149</v>
+        <v>90.708</v>
       </c>
       <c r="G13">
         <v>32</v>
@@ -2341,28 +2341,28 @@
         <v>104.4</v>
       </c>
       <c r="M13">
-        <v>4.1823947</v>
+        <v>4.5626124</v>
       </c>
       <c r="N13">
-        <v>100.2176053</v>
+        <v>99.8373876</v>
       </c>
       <c r="O13">
-        <v>24.052225272</v>
+        <v>23.960973024</v>
       </c>
       <c r="P13">
-        <v>76.165380028</v>
+        <v>75.876414576</v>
       </c>
       <c r="Q13">
-        <v>161.765380028</v>
+        <v>161.476414576</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1644132906765094</v>
+        <v>0.1654654553338512</v>
       </c>
       <c r="T13">
-        <v>0.5827912432016522</v>
+        <v>0.5879609197632564</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.96177608488266</v>
+        <v>22.88162807780911</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1501969606937891</v>
+        <v>0.1498610126854849</v>
       </c>
       <c r="C14">
-        <v>880.817286496952</v>
+        <v>876.2914267730714</v>
       </c>
       <c r="D14">
-        <v>939.5252864969519</v>
+        <v>942.5584267730715</v>
       </c>
       <c r="E14">
-        <v>-236.992</v>
+        <v>-229.433</v>
       </c>
       <c r="F14">
-        <v>90.708</v>
+        <v>98.267</v>
       </c>
       <c r="G14">
         <v>32</v>
@@ -2423,28 +2423,28 @@
         <v>104.4</v>
       </c>
       <c r="M14">
-        <v>4.5626124</v>
+        <v>4.942830099999999</v>
       </c>
       <c r="N14">
-        <v>99.8373876</v>
+        <v>99.45716990000001</v>
       </c>
       <c r="O14">
-        <v>23.960973024</v>
+        <v>23.869720776</v>
       </c>
       <c r="P14">
-        <v>75.876414576</v>
+        <v>75.58744912400002</v>
       </c>
       <c r="Q14">
-        <v>161.476414576</v>
+        <v>161.187449124</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1654654553338512</v>
+        <v>0.1665418076844654</v>
       </c>
       <c r="T14">
-        <v>0.5879609197632564</v>
+        <v>0.5932494394642079</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.88162807780911</v>
+        <v>21.12150284105457</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1498610126854849</v>
+        <v>0.1495250646771806</v>
       </c>
       <c r="C15">
-        <v>876.2914267730714</v>
+        <v>871.7852147098184</v>
       </c>
       <c r="D15">
-        <v>942.5584267730715</v>
+        <v>945.6112147098185</v>
       </c>
       <c r="E15">
-        <v>-229.433</v>
+        <v>-221.874</v>
       </c>
       <c r="F15">
-        <v>98.267</v>
+        <v>105.826</v>
       </c>
       <c r="G15">
         <v>32</v>
@@ -2505,28 +2505,28 @@
         <v>104.4</v>
       </c>
       <c r="M15">
-        <v>4.942830099999999</v>
+        <v>5.3230478</v>
       </c>
       <c r="N15">
-        <v>99.45716990000001</v>
+        <v>99.07695220000001</v>
       </c>
       <c r="O15">
-        <v>23.869720776</v>
+        <v>23.778468528</v>
       </c>
       <c r="P15">
-        <v>75.58744912400002</v>
+        <v>75.298483672</v>
       </c>
       <c r="Q15">
-        <v>161.187449124</v>
+        <v>160.898483672</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1665418076844654</v>
+        <v>0.1676431914850937</v>
       </c>
       <c r="T15">
-        <v>0.5932494394642079</v>
+        <v>0.598660947995414</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.12150284105457</v>
+        <v>19.61282406669352</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1495250646771806</v>
+        <v>0.1491891166688764</v>
       </c>
       <c r="C16">
-        <v>871.7852147098184</v>
+        <v>867.298841833903</v>
       </c>
       <c r="D16">
-        <v>945.6112147098185</v>
+        <v>948.683841833903</v>
       </c>
       <c r="E16">
-        <v>-221.874</v>
+        <v>-214.315</v>
       </c>
       <c r="F16">
-        <v>105.826</v>
+        <v>113.385</v>
       </c>
       <c r="G16">
         <v>32</v>
@@ -2587,28 +2587,28 @@
         <v>104.4</v>
       </c>
       <c r="M16">
-        <v>5.3230478</v>
+        <v>5.703265500000001</v>
       </c>
       <c r="N16">
-        <v>99.07695220000001</v>
+        <v>98.69673450000001</v>
       </c>
       <c r="O16">
-        <v>23.778468528</v>
+        <v>23.68721628</v>
       </c>
       <c r="P16">
-        <v>75.298483672</v>
+        <v>75.00951822</v>
       </c>
       <c r="Q16">
-        <v>160.898483672</v>
+        <v>160.60951822</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1676431914850937</v>
+        <v>0.1687704901986781</v>
       </c>
       <c r="T16">
-        <v>0.598660947995414</v>
+        <v>0.6041997861391193</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.61282406669352</v>
+        <v>18.30530246224729</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1491891166688763</v>
+        <v>0.1488531686605721</v>
       </c>
       <c r="C17">
-        <v>867.2988418339031</v>
+        <v>862.832502169504</v>
       </c>
       <c r="D17">
-        <v>948.6838418339031</v>
+        <v>951.7765021695039</v>
       </c>
       <c r="E17">
-        <v>-214.315</v>
+        <v>-206.756</v>
       </c>
       <c r="F17">
-        <v>113.385</v>
+        <v>120.944</v>
       </c>
       <c r="G17">
         <v>32</v>
@@ -2669,28 +2669,28 @@
         <v>104.4</v>
       </c>
       <c r="M17">
-        <v>5.7032655</v>
+        <v>6.0834832</v>
       </c>
       <c r="N17">
-        <v>98.69673450000001</v>
+        <v>98.3165168</v>
       </c>
       <c r="O17">
-        <v>23.68721628</v>
+        <v>23.595964032</v>
       </c>
       <c r="P17">
-        <v>75.00951822</v>
+        <v>74.720552768</v>
       </c>
       <c r="Q17">
-        <v>160.60951822</v>
+        <v>160.320552768</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.168770490198678</v>
+        <v>0.1699246293578239</v>
       </c>
       <c r="T17">
-        <v>0.6041997861391192</v>
+        <v>0.609870501381484</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.30530246224729</v>
+        <v>17.16122105835683</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1488531686605721</v>
+        <v>0.1485172206522678</v>
       </c>
       <c r="C18">
-        <v>862.832502169504</v>
+        <v>858.3863922791098</v>
       </c>
       <c r="D18">
-        <v>951.7765021695039</v>
+        <v>954.8893922791099</v>
       </c>
       <c r="E18">
-        <v>-206.756</v>
+        <v>-199.197</v>
       </c>
       <c r="F18">
-        <v>120.944</v>
+        <v>128.503</v>
       </c>
       <c r="G18">
         <v>32</v>
@@ -2751,28 +2751,28 @@
         <v>104.4</v>
       </c>
       <c r="M18">
-        <v>6.0834832</v>
+        <v>6.4637009</v>
       </c>
       <c r="N18">
-        <v>98.3165168</v>
+        <v>97.9362991</v>
       </c>
       <c r="O18">
-        <v>23.595964032</v>
+        <v>23.504711784</v>
       </c>
       <c r="P18">
-        <v>74.720552768</v>
+        <v>74.43158731600001</v>
       </c>
       <c r="Q18">
-        <v>160.320552768</v>
+        <v>160.031587316</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1699246293578239</v>
+        <v>0.1711065790991179</v>
       </c>
       <c r="T18">
-        <v>0.609870501381484</v>
+        <v>0.6156778603646287</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.16122105835683</v>
+        <v>16.15173746668878</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1485172206522678</v>
+        <v>0.1481812726439636</v>
       </c>
       <c r="C19">
-        <v>858.3863922791098</v>
+        <v>853.960711305164</v>
       </c>
       <c r="D19">
-        <v>954.8893922791099</v>
+        <v>958.022711305164</v>
       </c>
       <c r="E19">
-        <v>-199.197</v>
+        <v>-191.638</v>
       </c>
       <c r="F19">
-        <v>128.503</v>
+        <v>136.062</v>
       </c>
       <c r="G19">
         <v>32</v>
@@ -2833,28 +2833,28 @@
         <v>104.4</v>
       </c>
       <c r="M19">
-        <v>6.4637009</v>
+        <v>6.8439186</v>
       </c>
       <c r="N19">
-        <v>97.9362991</v>
+        <v>97.55608140000001</v>
       </c>
       <c r="O19">
-        <v>23.504711784</v>
+        <v>23.413459536</v>
       </c>
       <c r="P19">
-        <v>74.43158731600001</v>
+        <v>74.14262186400001</v>
       </c>
       <c r="Q19">
-        <v>160.031587316</v>
+        <v>159.742621864</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1711065790991179</v>
+        <v>0.1723173568828824</v>
       </c>
       <c r="T19">
-        <v>0.6156778603646287</v>
+        <v>0.6216268622498013</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.15173746668878</v>
+        <v>15.25441871853941</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1481812726439636</v>
+        <v>0.1478453246356593</v>
       </c>
       <c r="C20">
-        <v>853.9607113051643</v>
+        <v>849.5556610125354</v>
       </c>
       <c r="D20">
-        <v>958.0227113051643</v>
+        <v>961.1766610125354</v>
       </c>
       <c r="E20">
-        <v>-191.638</v>
+        <v>-184.079</v>
       </c>
       <c r="F20">
-        <v>136.062</v>
+        <v>143.621</v>
       </c>
       <c r="G20">
         <v>32</v>
@@ -2915,28 +2915,28 @@
         <v>104.4</v>
       </c>
       <c r="M20">
-        <v>6.843918599999999</v>
+        <v>7.224136300000001</v>
       </c>
       <c r="N20">
-        <v>97.55608140000001</v>
+        <v>97.17586370000001</v>
       </c>
       <c r="O20">
-        <v>23.413459536</v>
+        <v>23.322207288</v>
       </c>
       <c r="P20">
-        <v>74.14262186400001</v>
+        <v>73.85365641200001</v>
       </c>
       <c r="Q20">
-        <v>159.742621864</v>
+        <v>159.453656412</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1723173568828824</v>
+        <v>0.1735580304143942</v>
       </c>
       <c r="T20">
-        <v>0.6216268622498011</v>
+        <v>0.6277227530704101</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.25441871853941</v>
+        <v>14.45155457545838</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1478453246356593</v>
+        <v>0.1475093766273551</v>
       </c>
       <c r="C21">
-        <v>849.5556610125354</v>
+        <v>845.1714458318227</v>
       </c>
       <c r="D21">
-        <v>961.1766610125354</v>
+        <v>964.3514458318226</v>
       </c>
       <c r="E21">
-        <v>-184.079</v>
+        <v>-176.52</v>
       </c>
       <c r="F21">
-        <v>143.621</v>
+        <v>151.18</v>
       </c>
       <c r="G21">
         <v>32</v>
@@ -2997,28 +2997,28 @@
         <v>104.4</v>
       </c>
       <c r="M21">
-        <v>7.224136300000001</v>
+        <v>7.604354</v>
       </c>
       <c r="N21">
-        <v>97.17586370000001</v>
+        <v>96.795646</v>
       </c>
       <c r="O21">
-        <v>23.322207288</v>
+        <v>23.23095504</v>
       </c>
       <c r="P21">
-        <v>73.85365641200001</v>
+        <v>73.56469096000001</v>
       </c>
       <c r="Q21">
-        <v>159.453656412</v>
+        <v>159.16469096</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1735580304143942</v>
+        <v>0.1748297207841938</v>
       </c>
       <c r="T21">
-        <v>0.6277227530704101</v>
+        <v>0.6339710411615342</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.45155457545838</v>
+        <v>13.72897684668547</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1475093766273551</v>
+        <v>0.1471734286190508</v>
       </c>
       <c r="C22">
-        <v>845.1714458318227</v>
+        <v>840.8082729035295</v>
       </c>
       <c r="D22">
-        <v>964.3514458318226</v>
+        <v>967.5472729035296</v>
       </c>
       <c r="E22">
-        <v>-176.52</v>
+        <v>-168.961</v>
       </c>
       <c r="F22">
-        <v>151.18</v>
+        <v>158.739</v>
       </c>
       <c r="G22">
         <v>32</v>
@@ -3079,28 +3079,28 @@
         <v>104.4</v>
       </c>
       <c r="M22">
-        <v>7.604354</v>
+        <v>7.9845717</v>
       </c>
       <c r="N22">
-        <v>96.795646</v>
+        <v>96.4154283</v>
       </c>
       <c r="O22">
-        <v>23.23095504</v>
+        <v>23.139702792</v>
       </c>
       <c r="P22">
-        <v>73.56469096000001</v>
+        <v>73.27572550799999</v>
       </c>
       <c r="Q22">
-        <v>159.16469096</v>
+        <v>158.875725508</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1748297207841938</v>
+        <v>0.1761336058468997</v>
       </c>
       <c r="T22">
-        <v>0.6339710411615342</v>
+        <v>0.6403775137612945</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.72897684668547</v>
+        <v>13.07521604446235</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1471734286190508</v>
+        <v>0.1470882806107466</v>
       </c>
       <c r="C23">
-        <v>840.80827290353</v>
+        <v>834.0626416637771</v>
       </c>
       <c r="D23">
-        <v>967.5472729035299</v>
+        <v>968.3606416637771</v>
       </c>
       <c r="E23">
-        <v>-168.961</v>
+        <v>-161.402</v>
       </c>
       <c r="F23">
-        <v>158.739</v>
+        <v>166.298</v>
       </c>
       <c r="G23">
         <v>32</v>
@@ -3161,45 +3161,45 @@
         <v>104.4</v>
       </c>
       <c r="M23">
-        <v>7.984571699999998</v>
+        <v>8.614236399999999</v>
       </c>
       <c r="N23">
-        <v>96.4154283</v>
+        <v>95.78576360000001</v>
       </c>
       <c r="O23">
-        <v>23.139702792</v>
+        <v>22.988583264</v>
       </c>
       <c r="P23">
-        <v>73.27572550799999</v>
+        <v>72.79718033600001</v>
       </c>
       <c r="Q23">
-        <v>158.875725508</v>
+        <v>158.397180336</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1761336058468997</v>
+        <v>0.1774709238599315</v>
       </c>
       <c r="T23">
-        <v>0.6403775137612945</v>
+        <v>0.6469482548892538</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.07521604446235</v>
+        <v>12.11947236553666</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1470882806107466</v>
+        <v>0.1467637326024423</v>
       </c>
       <c r="C24">
-        <v>834.0626416637771</v>
+        <v>829.6164378082076</v>
       </c>
       <c r="D24">
-        <v>968.3606416637771</v>
+        <v>971.4734378082076</v>
       </c>
       <c r="E24">
-        <v>-161.402</v>
+        <v>-153.843</v>
       </c>
       <c r="F24">
-        <v>166.298</v>
+        <v>173.857</v>
       </c>
       <c r="G24">
         <v>32</v>
@@ -3243,28 +3243,28 @@
         <v>104.4</v>
       </c>
       <c r="M24">
-        <v>8.614236399999999</v>
+        <v>9.005792599999999</v>
       </c>
       <c r="N24">
-        <v>95.78576360000001</v>
+        <v>95.3942074</v>
       </c>
       <c r="O24">
-        <v>22.988583264</v>
+        <v>22.894609776</v>
       </c>
       <c r="P24">
-        <v>72.79718033600001</v>
+        <v>72.499597624</v>
       </c>
       <c r="Q24">
-        <v>158.397180336</v>
+        <v>158.099597624</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1774709238599315</v>
+        <v>0.1788429774057692</v>
       </c>
       <c r="T24">
-        <v>0.6469482548892538</v>
+        <v>0.6536896646179392</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.11947236553666</v>
+        <v>11.59253878442637</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1467637326024423</v>
+        <v>0.146439184594138</v>
       </c>
       <c r="C25">
-        <v>829.6164378082076</v>
+        <v>825.1903106611887</v>
       </c>
       <c r="D25">
-        <v>971.4734378082076</v>
+        <v>974.6063106611888</v>
       </c>
       <c r="E25">
-        <v>-153.843</v>
+        <v>-146.284</v>
       </c>
       <c r="F25">
-        <v>173.857</v>
+        <v>181.416</v>
       </c>
       <c r="G25">
         <v>32</v>
@@ -3325,28 +3325,28 @@
         <v>104.4</v>
       </c>
       <c r="M25">
-        <v>9.005792599999999</v>
+        <v>9.3973488</v>
       </c>
       <c r="N25">
-        <v>95.3942074</v>
+        <v>95.0026512</v>
       </c>
       <c r="O25">
-        <v>22.894609776</v>
+        <v>22.800636288</v>
       </c>
       <c r="P25">
-        <v>72.499597624</v>
+        <v>72.20201491200001</v>
       </c>
       <c r="Q25">
-        <v>158.099597624</v>
+        <v>157.802014912</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1788429774057692</v>
+        <v>0.1802511376238658</v>
       </c>
       <c r="T25">
-        <v>0.6536896646179392</v>
+        <v>0.6606084798658004</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.59253878442637</v>
+        <v>11.10951633507527</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.146439184594138</v>
+        <v>0.1461146365858338</v>
       </c>
       <c r="C26">
-        <v>825.1903106611887</v>
+        <v>820.7844550852852</v>
       </c>
       <c r="D26">
-        <v>974.6063106611888</v>
+        <v>977.7594550852853</v>
       </c>
       <c r="E26">
-        <v>-146.284</v>
+        <v>-138.725</v>
       </c>
       <c r="F26">
-        <v>181.416</v>
+        <v>188.975</v>
       </c>
       <c r="G26">
         <v>32</v>
@@ -3407,28 +3407,28 @@
         <v>104.4</v>
       </c>
       <c r="M26">
-        <v>9.3973488</v>
+        <v>9.788905</v>
       </c>
       <c r="N26">
-        <v>95.0026512</v>
+        <v>94.61109500000001</v>
       </c>
       <c r="O26">
-        <v>22.800636288</v>
+        <v>22.7066628</v>
       </c>
       <c r="P26">
-        <v>72.20201491200001</v>
+        <v>71.9044322</v>
       </c>
       <c r="Q26">
-        <v>157.802014912</v>
+        <v>157.5044322</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1802511376238658</v>
+        <v>0.1816968487811117</v>
       </c>
       <c r="T26">
-        <v>0.6606084798658004</v>
+        <v>0.6677117968536048</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.10951633507527</v>
+        <v>10.66513568167226</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1461146365858338</v>
+        <v>0.1457900885775295</v>
       </c>
       <c r="C27">
-        <v>820.7844550852852</v>
+        <v>816.3990684730015</v>
       </c>
       <c r="D27">
-        <v>977.7594550852853</v>
+        <v>980.9330684730015</v>
       </c>
       <c r="E27">
-        <v>-138.725</v>
+        <v>-131.166</v>
       </c>
       <c r="F27">
-        <v>188.975</v>
+        <v>196.534</v>
       </c>
       <c r="G27">
         <v>32</v>
@@ -3489,28 +3489,28 @@
         <v>104.4</v>
       </c>
       <c r="M27">
-        <v>9.788905</v>
+        <v>10.1804612</v>
       </c>
       <c r="N27">
-        <v>94.61109500000001</v>
+        <v>94.21953880000001</v>
       </c>
       <c r="O27">
-        <v>22.7066628</v>
+        <v>22.612689312</v>
       </c>
       <c r="P27">
-        <v>71.9044322</v>
+        <v>71.60684948800001</v>
       </c>
       <c r="Q27">
-        <v>157.5044322</v>
+        <v>157.206849488</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1816968487811117</v>
+        <v>0.1831816332128777</v>
       </c>
       <c r="T27">
-        <v>0.6677117968536048</v>
+        <v>0.67500709538162</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.66513568167226</v>
+        <v>10.2549381554541</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1457900885775295</v>
+        <v>0.1454655405692253</v>
       </c>
       <c r="C28">
-        <v>816.3990684730015</v>
+        <v>812.0343507879761</v>
       </c>
       <c r="D28">
-        <v>980.9330684730015</v>
+        <v>984.1273507879762</v>
       </c>
       <c r="E28">
-        <v>-131.166</v>
+        <v>-123.607</v>
       </c>
       <c r="F28">
-        <v>196.534</v>
+        <v>204.093</v>
       </c>
       <c r="G28">
         <v>32</v>
@@ -3571,28 +3571,28 @@
         <v>104.4</v>
       </c>
       <c r="M28">
-        <v>10.1804612</v>
+        <v>10.5720174</v>
       </c>
       <c r="N28">
-        <v>94.21953880000001</v>
+        <v>93.82798260000001</v>
       </c>
       <c r="O28">
-        <v>22.612689312</v>
+        <v>22.518715824</v>
       </c>
       <c r="P28">
-        <v>71.60684948800001</v>
+        <v>71.30926677600002</v>
       </c>
       <c r="Q28">
-        <v>157.206849488</v>
+        <v>156.909266776</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1831816332128777</v>
+        <v>0.1847070966701716</v>
       </c>
       <c r="T28">
-        <v>0.67500709538162</v>
+        <v>0.6825022651021836</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.2549381554541</v>
+        <v>9.875125631178021</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1454655405692253</v>
+        <v>0.145502752560921</v>
       </c>
       <c r="C29">
-        <v>812.0343507879761</v>
+        <v>804.108045594645</v>
       </c>
       <c r="D29">
-        <v>984.1273507879762</v>
+        <v>983.760045594645</v>
       </c>
       <c r="E29">
-        <v>-123.607</v>
+        <v>-116.048</v>
       </c>
       <c r="F29">
-        <v>204.093</v>
+        <v>211.652</v>
       </c>
       <c r="G29">
         <v>32</v>
@@ -3653,45 +3653,45 @@
         <v>104.4</v>
       </c>
       <c r="M29">
-        <v>10.5720174</v>
+        <v>11.323382</v>
       </c>
       <c r="N29">
-        <v>93.82798260000001</v>
+        <v>93.07661800000001</v>
       </c>
       <c r="O29">
-        <v>22.518715824</v>
+        <v>22.33838832</v>
       </c>
       <c r="P29">
-        <v>71.30926677600002</v>
+        <v>70.73822968000002</v>
       </c>
       <c r="Q29">
-        <v>156.909266776</v>
+        <v>156.33822968</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1847070966701716</v>
+        <v>0.1862749341123903</v>
       </c>
       <c r="T29">
-        <v>0.6825022651021836</v>
+        <v>0.6902056339816517</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.24</v>
       </c>
       <c r="W29">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>9.875125631178021</v>
+        <v>9.219860285557797</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.145502752560921</v>
+        <v>0.1451911245526167</v>
       </c>
       <c r="C30">
-        <v>804.108045594645</v>
+        <v>799.6334979040226</v>
       </c>
       <c r="D30">
-        <v>983.760045594645</v>
+        <v>986.8444979040227</v>
       </c>
       <c r="E30">
-        <v>-116.048</v>
+        <v>-108.489</v>
       </c>
       <c r="F30">
-        <v>211.652</v>
+        <v>219.211</v>
       </c>
       <c r="G30">
         <v>32</v>
@@ -3735,28 +3735,28 @@
         <v>104.4</v>
       </c>
       <c r="M30">
-        <v>11.323382</v>
+        <v>11.7277885</v>
       </c>
       <c r="N30">
-        <v>93.07661800000001</v>
+        <v>92.6722115</v>
       </c>
       <c r="O30">
-        <v>22.33838832</v>
+        <v>22.24133076</v>
       </c>
       <c r="P30">
-        <v>70.73822968000002</v>
+        <v>70.43088074000001</v>
       </c>
       <c r="Q30">
-        <v>156.33822968</v>
+        <v>156.03088074</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1862749341123903</v>
+        <v>0.187886935989601</v>
       </c>
       <c r="T30">
-        <v>0.6902056339816517</v>
+        <v>0.6981259991675838</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.219860285557797</v>
+        <v>8.901934068814423</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1451911245526167</v>
+        <v>0.1448794965443125</v>
       </c>
       <c r="C31">
-        <v>799.6334979040226</v>
+        <v>795.1783528499378</v>
       </c>
       <c r="D31">
-        <v>986.8444979040227</v>
+        <v>989.9483528499378</v>
       </c>
       <c r="E31">
-        <v>-108.489</v>
+        <v>-100.93</v>
       </c>
       <c r="F31">
-        <v>219.211</v>
+        <v>226.77</v>
       </c>
       <c r="G31">
         <v>32</v>
@@ -3817,28 +3817,28 @@
         <v>104.4</v>
       </c>
       <c r="M31">
-        <v>11.7277885</v>
+        <v>12.132195</v>
       </c>
       <c r="N31">
-        <v>92.6722115</v>
+        <v>92.26780500000001</v>
       </c>
       <c r="O31">
-        <v>22.24133076</v>
+        <v>22.1442732</v>
       </c>
       <c r="P31">
-        <v>70.43088074000001</v>
+        <v>70.12353180000001</v>
       </c>
       <c r="Q31">
-        <v>156.03088074</v>
+        <v>155.7235318</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.187886935989601</v>
+        <v>0.1895449950633036</v>
       </c>
       <c r="T31">
-        <v>0.6981259991675838</v>
+        <v>0.7062726605016852</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.901934068814423</v>
+        <v>8.605202933187277</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1448794965443125</v>
+        <v>0.1445678685360082</v>
       </c>
       <c r="C32">
-        <v>795.1783528499378</v>
+        <v>790.7427940874111</v>
       </c>
       <c r="D32">
-        <v>989.9483528499378</v>
+        <v>993.0717940874109</v>
       </c>
       <c r="E32">
-        <v>-100.93</v>
+        <v>-93.37100000000001</v>
       </c>
       <c r="F32">
-        <v>226.77</v>
+        <v>234.329</v>
       </c>
       <c r="G32">
         <v>32</v>
@@ -3899,28 +3899,28 @@
         <v>104.4</v>
       </c>
       <c r="M32">
-        <v>12.132195</v>
+        <v>12.5366015</v>
       </c>
       <c r="N32">
-        <v>92.26780500000001</v>
+        <v>91.8633985</v>
       </c>
       <c r="O32">
-        <v>22.1442732</v>
+        <v>22.04721564</v>
       </c>
       <c r="P32">
-        <v>70.12353180000001</v>
+        <v>69.81618286</v>
       </c>
       <c r="Q32">
-        <v>155.7235318</v>
+        <v>155.41618286</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1895449950633036</v>
+        <v>0.1912511138203018</v>
       </c>
       <c r="T32">
-        <v>0.7062726605016852</v>
+        <v>0.7146554569469202</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.605202933187277</v>
+        <v>8.327615741794139</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1445678685360082</v>
+        <v>0.144256240527704</v>
       </c>
       <c r="C33">
-        <v>790.7427940874111</v>
+        <v>786.3270075966401</v>
       </c>
       <c r="D33">
-        <v>993.0717940874109</v>
+        <v>996.2150075966401</v>
       </c>
       <c r="E33">
-        <v>-93.37100000000001</v>
+        <v>-85.81199999999998</v>
       </c>
       <c r="F33">
-        <v>234.329</v>
+        <v>241.888</v>
       </c>
       <c r="G33">
         <v>32</v>
@@ -3981,28 +3981,28 @@
         <v>104.4</v>
       </c>
       <c r="M33">
-        <v>12.5366015</v>
+        <v>12.941008</v>
       </c>
       <c r="N33">
-        <v>91.8633985</v>
+        <v>91.45899200000001</v>
       </c>
       <c r="O33">
-        <v>22.04721564</v>
+        <v>21.95015808</v>
       </c>
       <c r="P33">
-        <v>69.81618286</v>
+        <v>69.50883392</v>
       </c>
       <c r="Q33">
-        <v>155.41618286</v>
+        <v>155.10883392</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1912511138203018</v>
+        <v>0.1930074125407412</v>
       </c>
       <c r="T33">
-        <v>0.7146554569469202</v>
+        <v>0.7232848062287797</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.327615741794139</v>
+        <v>8.067377749863072</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.144256240527704</v>
+        <v>0.1439446125193997</v>
       </c>
       <c r="C34">
-        <v>786.3270075966401</v>
+        <v>781.9311817199147</v>
       </c>
       <c r="D34">
-        <v>996.2150075966401</v>
+        <v>999.3781817199147</v>
       </c>
       <c r="E34">
-        <v>-85.81199999999998</v>
+        <v>-78.25299999999999</v>
       </c>
       <c r="F34">
-        <v>241.888</v>
+        <v>249.447</v>
       </c>
       <c r="G34">
         <v>32</v>
@@ -4063,28 +4063,28 @@
         <v>104.4</v>
       </c>
       <c r="M34">
-        <v>12.941008</v>
+        <v>13.3454145</v>
       </c>
       <c r="N34">
-        <v>91.45899200000001</v>
+        <v>91.0545855</v>
       </c>
       <c r="O34">
-        <v>21.95015808</v>
+        <v>21.85310052</v>
       </c>
       <c r="P34">
-        <v>69.50883392</v>
+        <v>69.20148498</v>
       </c>
       <c r="Q34">
-        <v>155.10883392</v>
+        <v>154.80148498</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1930074125407412</v>
+        <v>0.1948161380886563</v>
       </c>
       <c r="T34">
-        <v>0.7232848062287797</v>
+        <v>0.7321717480265154</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.067377749863072</v>
+        <v>7.822911757442978</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1439446125193997</v>
+        <v>0.1438397045110955</v>
       </c>
       <c r="C35">
-        <v>781.9311817199147</v>
+        <v>775.4415726887039</v>
       </c>
       <c r="D35">
-        <v>999.3781817199147</v>
+        <v>1000.447572688704</v>
       </c>
       <c r="E35">
-        <v>-78.25299999999999</v>
+        <v>-70.69399999999996</v>
       </c>
       <c r="F35">
-        <v>249.447</v>
+        <v>257.006</v>
       </c>
       <c r="G35">
         <v>32</v>
@@ -4145,45 +4145,45 @@
         <v>104.4</v>
       </c>
       <c r="M35">
-        <v>13.3454145</v>
+        <v>13.9554258</v>
       </c>
       <c r="N35">
-        <v>91.0545855</v>
+        <v>90.44457420000001</v>
       </c>
       <c r="O35">
-        <v>21.85310052</v>
+        <v>21.706697808</v>
       </c>
       <c r="P35">
-        <v>69.20148498</v>
+        <v>68.737876392</v>
       </c>
       <c r="Q35">
-        <v>154.80148498</v>
+        <v>154.337876392</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1948161380886563</v>
+        <v>0.1966796735016598</v>
       </c>
       <c r="T35">
-        <v>0.7321717480265154</v>
+        <v>0.7413279910908495</v>
       </c>
       <c r="U35">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.24</v>
       </c>
       <c r="W35">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.822911757442978</v>
+        <v>7.480961276007787</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1438397045110955</v>
+        <v>0.1435341565027912</v>
       </c>
       <c r="C36">
-        <v>775.4415726887039</v>
+        <v>771.0102894889112</v>
       </c>
       <c r="D36">
-        <v>1000.447572688704</v>
+        <v>1003.575289488911</v>
       </c>
       <c r="E36">
-        <v>-70.69399999999996</v>
+        <v>-63.13499999999999</v>
       </c>
       <c r="F36">
-        <v>257.006</v>
+        <v>264.565</v>
       </c>
       <c r="G36">
         <v>32</v>
@@ -4227,28 +4227,28 @@
         <v>104.4</v>
       </c>
       <c r="M36">
-        <v>13.9554258</v>
+        <v>14.3658795</v>
       </c>
       <c r="N36">
-        <v>90.44457420000001</v>
+        <v>90.0341205</v>
       </c>
       <c r="O36">
-        <v>21.706697808</v>
+        <v>21.60818892</v>
       </c>
       <c r="P36">
-        <v>68.737876392</v>
+        <v>68.42593158</v>
       </c>
       <c r="Q36">
-        <v>154.337876392</v>
+        <v>154.02593158</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1966796735016598</v>
+        <v>0.1986005484658326</v>
       </c>
       <c r="T36">
-        <v>0.7413279910908495</v>
+        <v>0.750765964711009</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.480961276007787</v>
+        <v>7.267219525264708</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1435341565027912</v>
+        <v>0.1432286084944869</v>
       </c>
       <c r="C37">
-        <v>771.0102894889112</v>
+        <v>766.5986240924233</v>
       </c>
       <c r="D37">
-        <v>1003.575289488911</v>
+        <v>1006.722624092423</v>
       </c>
       <c r="E37">
-        <v>-63.13499999999999</v>
+        <v>-55.57599999999996</v>
       </c>
       <c r="F37">
-        <v>264.565</v>
+        <v>272.124</v>
       </c>
       <c r="G37">
         <v>32</v>
@@ -4309,28 +4309,28 @@
         <v>104.4</v>
       </c>
       <c r="M37">
-        <v>14.3658795</v>
+        <v>14.7763332</v>
       </c>
       <c r="N37">
-        <v>90.0341205</v>
+        <v>89.62366680000001</v>
       </c>
       <c r="O37">
-        <v>21.60818892</v>
+        <v>21.509680032</v>
       </c>
       <c r="P37">
-        <v>68.42593158</v>
+        <v>68.113986768</v>
       </c>
       <c r="Q37">
-        <v>154.02593158</v>
+        <v>153.713986768</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1986005484658326</v>
+        <v>0.2005814507726359</v>
       </c>
       <c r="T37">
-        <v>0.750765964711009</v>
+        <v>0.7604988750067986</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.267219525264708</v>
+        <v>7.065352316229577</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.143228608494487</v>
+        <v>0.1429230604861827</v>
       </c>
       <c r="C38">
-        <v>766.5986240924228</v>
+        <v>762.2067616513762</v>
       </c>
       <c r="D38">
-        <v>1006.722624092423</v>
+        <v>1009.889761651376</v>
       </c>
       <c r="E38">
-        <v>-55.57600000000002</v>
+        <v>-48.017</v>
       </c>
       <c r="F38">
-        <v>272.124</v>
+        <v>279.683</v>
       </c>
       <c r="G38">
         <v>32</v>
@@ -4391,28 +4391,28 @@
         <v>104.4</v>
       </c>
       <c r="M38">
-        <v>14.7763332</v>
+        <v>15.1867869</v>
       </c>
       <c r="N38">
-        <v>89.62366680000001</v>
+        <v>89.2132131</v>
       </c>
       <c r="O38">
-        <v>21.509680032</v>
+        <v>21.411171144</v>
       </c>
       <c r="P38">
-        <v>68.113986768</v>
+        <v>67.80204195600001</v>
       </c>
       <c r="Q38">
-        <v>153.713986768</v>
+        <v>153.402041956</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2005814507726359</v>
+        <v>0.2026252388669567</v>
       </c>
       <c r="T38">
-        <v>0.7604988750067985</v>
+        <v>0.7705407665818195</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.065352316229578</v>
+        <v>6.874396848223373</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1429230604861827</v>
+        <v>0.1426175124778784</v>
       </c>
       <c r="C39">
-        <v>762.2067616513762</v>
+        <v>757.8348896552068</v>
       </c>
       <c r="D39">
-        <v>1009.889761651376</v>
+        <v>1013.076889655207</v>
       </c>
       <c r="E39">
-        <v>-48.017</v>
+        <v>-40.45799999999997</v>
       </c>
       <c r="F39">
-        <v>279.683</v>
+        <v>287.242</v>
       </c>
       <c r="G39">
         <v>32</v>
@@ -4473,28 +4473,28 @@
         <v>104.4</v>
       </c>
       <c r="M39">
-        <v>15.1867869</v>
+        <v>15.5972406</v>
       </c>
       <c r="N39">
-        <v>89.2132131</v>
+        <v>88.8027594</v>
       </c>
       <c r="O39">
-        <v>21.411171144</v>
+        <v>21.312662256</v>
       </c>
       <c r="P39">
-        <v>67.80204195600001</v>
+        <v>67.490097144</v>
       </c>
       <c r="Q39">
-        <v>153.402041956</v>
+        <v>153.090097144</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2026252388669567</v>
+        <v>0.2047349556094814</v>
       </c>
       <c r="T39">
-        <v>0.7705407665818195</v>
+        <v>0.7809065901431315</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.874396848223373</v>
+        <v>6.693491668006968</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1426175124778784</v>
+        <v>0.1423119644695742</v>
       </c>
       <c r="C40">
-        <v>757.8348896552068</v>
+        <v>753.4831979676471</v>
       </c>
       <c r="D40">
-        <v>1013.076889655207</v>
+        <v>1016.284197967647</v>
       </c>
       <c r="E40">
-        <v>-40.45799999999997</v>
+        <v>-32.899</v>
       </c>
       <c r="F40">
-        <v>287.242</v>
+        <v>294.801</v>
       </c>
       <c r="G40">
         <v>32</v>
@@ -4555,28 +4555,28 @@
         <v>104.4</v>
       </c>
       <c r="M40">
-        <v>15.5972406</v>
+        <v>16.0076943</v>
       </c>
       <c r="N40">
-        <v>88.8027594</v>
+        <v>88.39230570000001</v>
       </c>
       <c r="O40">
-        <v>21.312662256</v>
+        <v>21.214153368</v>
       </c>
       <c r="P40">
-        <v>67.490097144</v>
+        <v>67.17815233200001</v>
       </c>
       <c r="Q40">
-        <v>153.090097144</v>
+        <v>152.778152332</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2047349556094814</v>
+        <v>0.2069138433927445</v>
       </c>
       <c r="T40">
-        <v>0.7809065901431315</v>
+        <v>0.7916122767720274</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.693491668006968</v>
+        <v>6.52186367651961</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1423119644695742</v>
+        <v>0.1420064164612699</v>
       </c>
       <c r="C41">
-        <v>753.4831979676471</v>
+        <v>749.1518788644308</v>
       </c>
       <c r="D41">
-        <v>1016.284197967647</v>
+        <v>1019.511878864431</v>
       </c>
       <c r="E41">
-        <v>-32.899</v>
+        <v>-25.33999999999997</v>
       </c>
       <c r="F41">
-        <v>294.801</v>
+        <v>302.36</v>
       </c>
       <c r="G41">
         <v>32</v>
@@ -4637,28 +4637,28 @@
         <v>104.4</v>
       </c>
       <c r="M41">
-        <v>16.0076943</v>
+        <v>16.418148</v>
       </c>
       <c r="N41">
-        <v>88.39230570000001</v>
+        <v>87.981852</v>
       </c>
       <c r="O41">
-        <v>21.214153368</v>
+        <v>21.11564448</v>
       </c>
       <c r="P41">
-        <v>67.17815233200001</v>
+        <v>66.86620752</v>
       </c>
       <c r="Q41">
-        <v>152.778152332</v>
+        <v>152.46620752</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2069138433927445</v>
+        <v>0.2091653607687832</v>
       </c>
       <c r="T41">
-        <v>0.7916122767720274</v>
+        <v>0.8026748196218867</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.52186367651961</v>
+        <v>6.358817084606619</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1420064164612699</v>
+        <v>0.1417008684529657</v>
       </c>
       <c r="C42">
-        <v>749.1518788644308</v>
+        <v>744.8411270717174</v>
       </c>
       <c r="D42">
-        <v>1019.511878864431</v>
+        <v>1022.760127071718</v>
       </c>
       <c r="E42">
-        <v>-25.33999999999997</v>
+        <v>-17.78099999999995</v>
       </c>
       <c r="F42">
-        <v>302.36</v>
+        <v>309.919</v>
       </c>
       <c r="G42">
         <v>32</v>
@@ -4719,28 +4719,28 @@
         <v>104.4</v>
       </c>
       <c r="M42">
-        <v>16.418148</v>
+        <v>16.8286017</v>
       </c>
       <c r="N42">
-        <v>87.981852</v>
+        <v>87.5713983</v>
       </c>
       <c r="O42">
-        <v>21.11564448</v>
+        <v>21.017135592</v>
       </c>
       <c r="P42">
-        <v>66.86620752</v>
+        <v>66.554262708</v>
       </c>
       <c r="Q42">
-        <v>152.46620752</v>
+        <v>152.154262708</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2091653607687832</v>
+        <v>0.2114932007677384</v>
       </c>
       <c r="T42">
-        <v>0.8026748196218867</v>
+        <v>0.8141123639242833</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.358817084606619</v>
+        <v>6.203723984982067</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1417008684529657</v>
+        <v>0.1417145204446614</v>
       </c>
       <c r="C43">
-        <v>744.8411270717174</v>
+        <v>737.1365525257906</v>
       </c>
       <c r="D43">
-        <v>1022.760127071718</v>
+        <v>1022.614552525791</v>
       </c>
       <c r="E43">
-        <v>-17.78099999999995</v>
+        <v>-10.22199999999998</v>
       </c>
       <c r="F43">
-        <v>309.919</v>
+        <v>317.478</v>
       </c>
       <c r="G43">
         <v>32</v>
@@ -4801,45 +4801,45 @@
         <v>104.4</v>
       </c>
       <c r="M43">
-        <v>16.8286017</v>
+        <v>17.5565334</v>
       </c>
       <c r="N43">
-        <v>87.5713983</v>
+        <v>86.8434666</v>
       </c>
       <c r="O43">
-        <v>21.017135592</v>
+        <v>20.842431984</v>
       </c>
       <c r="P43">
-        <v>66.554262708</v>
+        <v>66.001034616</v>
       </c>
       <c r="Q43">
-        <v>152.154262708</v>
+        <v>151.601034616</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2114932007677384</v>
+        <v>0.2139013111114852</v>
       </c>
       <c r="T43">
-        <v>0.8141123639242833</v>
+        <v>0.8259443063060732</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.24</v>
       </c>
       <c r="W43">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.203723984982067</v>
+        <v>5.946504222752766</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1417145204446614</v>
+        <v>0.1414165724363572</v>
       </c>
       <c r="C44">
-        <v>737.1365525257908</v>
+        <v>732.7640918612265</v>
       </c>
       <c r="D44">
-        <v>1022.614552525791</v>
+        <v>1025.801091861226</v>
       </c>
       <c r="E44">
-        <v>-10.22200000000004</v>
+        <v>-2.663000000000011</v>
       </c>
       <c r="F44">
-        <v>317.478</v>
+        <v>325.037</v>
       </c>
       <c r="G44">
         <v>32</v>
@@ -4883,28 +4883,28 @@
         <v>104.4</v>
       </c>
       <c r="M44">
-        <v>17.5565334</v>
+        <v>17.9745461</v>
       </c>
       <c r="N44">
-        <v>86.8434666</v>
+        <v>86.42545390000001</v>
       </c>
       <c r="O44">
-        <v>20.842431984</v>
+        <v>20.742108936</v>
       </c>
       <c r="P44">
-        <v>66.001034616</v>
+        <v>65.68334496400001</v>
       </c>
       <c r="Q44">
-        <v>151.601034616</v>
+        <v>151.283344964</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2139013111114852</v>
+        <v>0.2163939165550125</v>
       </c>
       <c r="T44">
-        <v>0.8259443063060731</v>
+        <v>0.838191404560908</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.946504222752767</v>
+        <v>5.808213426874797</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1414165724363572</v>
+        <v>0.1411186244280529</v>
       </c>
       <c r="C45">
-        <v>732.7640918612265</v>
+        <v>728.411552236314</v>
       </c>
       <c r="D45">
-        <v>1025.801091861226</v>
+        <v>1029.007552236314</v>
       </c>
       <c r="E45">
-        <v>-2.663000000000011</v>
+        <v>4.896000000000015</v>
       </c>
       <c r="F45">
-        <v>325.037</v>
+        <v>332.596</v>
       </c>
       <c r="G45">
         <v>32</v>
@@ -4965,28 +4965,28 @@
         <v>104.4</v>
       </c>
       <c r="M45">
-        <v>17.9745461</v>
+        <v>18.3925588</v>
       </c>
       <c r="N45">
-        <v>86.42545390000001</v>
+        <v>86.0074412</v>
       </c>
       <c r="O45">
-        <v>20.742108936</v>
+        <v>20.641785888</v>
       </c>
       <c r="P45">
-        <v>65.68334496400001</v>
+        <v>65.365655312</v>
       </c>
       <c r="Q45">
-        <v>151.283344964</v>
+        <v>150.965655312</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2163939165550125</v>
+        <v>0.218975543621523</v>
       </c>
       <c r="T45">
-        <v>0.838191404560908</v>
+        <v>0.8508758991819871</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.808213426874797</v>
+        <v>5.676208576264005</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1411186244280529</v>
+        <v>0.1408206764197487</v>
       </c>
       <c r="C46">
-        <v>728.411552236314</v>
+        <v>724.0791210450277</v>
       </c>
       <c r="D46">
-        <v>1029.007552236314</v>
+        <v>1032.234121045028</v>
       </c>
       <c r="E46">
-        <v>4.896000000000015</v>
+        <v>12.45499999999998</v>
       </c>
       <c r="F46">
-        <v>332.596</v>
+        <v>340.155</v>
       </c>
       <c r="G46">
         <v>32</v>
@@ -5047,28 +5047,28 @@
         <v>104.4</v>
       </c>
       <c r="M46">
-        <v>18.3925588</v>
+        <v>18.8105715</v>
       </c>
       <c r="N46">
-        <v>86.0074412</v>
+        <v>85.58942850000001</v>
       </c>
       <c r="O46">
-        <v>20.641785888</v>
+        <v>20.54146284</v>
       </c>
       <c r="P46">
-        <v>65.365655312</v>
+        <v>65.04796566000002</v>
       </c>
       <c r="Q46">
-        <v>150.965655312</v>
+        <v>150.64796566</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.218975543621523</v>
+        <v>0.2216510480359066</v>
       </c>
       <c r="T46">
-        <v>0.8508758991819871</v>
+        <v>0.8640216481529238</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.676208576264005</v>
+        <v>5.550070607902584</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1408206764197487</v>
+        <v>0.1405227284114444</v>
       </c>
       <c r="C47">
-        <v>724.0791210450277</v>
+        <v>719.7669880391156</v>
       </c>
       <c r="D47">
-        <v>1032.234121045028</v>
+        <v>1035.480988039116</v>
       </c>
       <c r="E47">
-        <v>12.45499999999998</v>
+        <v>20.01400000000001</v>
       </c>
       <c r="F47">
-        <v>340.155</v>
+        <v>347.714</v>
       </c>
       <c r="G47">
         <v>32</v>
@@ -5129,28 +5129,28 @@
         <v>104.4</v>
       </c>
       <c r="M47">
-        <v>18.8105715</v>
+        <v>19.2285842</v>
       </c>
       <c r="N47">
-        <v>85.58942850000001</v>
+        <v>85.17141580000001</v>
       </c>
       <c r="O47">
-        <v>20.54146284</v>
+        <v>20.441139792</v>
       </c>
       <c r="P47">
-        <v>65.04796566000002</v>
+        <v>64.730276008</v>
       </c>
       <c r="Q47">
-        <v>150.64796566</v>
+        <v>150.330276008</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2216510480359066</v>
+        <v>0.2244256452063785</v>
       </c>
       <c r="T47">
-        <v>0.8640216481529238</v>
+        <v>0.8776542767153764</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.550070607902584</v>
+        <v>5.429416899035136</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1405227284114444</v>
+        <v>0.1402247804031401</v>
       </c>
       <c r="C48">
-        <v>719.7669880391156</v>
+        <v>715.475345365296</v>
       </c>
       <c r="D48">
-        <v>1035.480988039116</v>
+        <v>1038.748345365296</v>
       </c>
       <c r="E48">
-        <v>20.01400000000001</v>
+        <v>27.57300000000004</v>
       </c>
       <c r="F48">
-        <v>347.714</v>
+        <v>355.273</v>
       </c>
       <c r="G48">
         <v>32</v>
@@ -5211,28 +5211,28 @@
         <v>104.4</v>
       </c>
       <c r="M48">
-        <v>19.2285842</v>
+        <v>19.6465969</v>
       </c>
       <c r="N48">
-        <v>85.17141580000001</v>
+        <v>84.7534031</v>
       </c>
       <c r="O48">
-        <v>20.441139792</v>
+        <v>20.340816744</v>
       </c>
       <c r="P48">
-        <v>64.730276008</v>
+        <v>64.41258635600001</v>
       </c>
       <c r="Q48">
-        <v>150.330276008</v>
+        <v>150.012586356</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2244256452063785</v>
+        <v>0.2273049441568682</v>
       </c>
       <c r="T48">
-        <v>0.8776542767153764</v>
+        <v>0.8918013440915066</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.429416899035136</v>
+        <v>5.313897390545026</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1402247804031401</v>
+        <v>0.1399268323948359</v>
       </c>
       <c r="C49">
-        <v>715.475345365296</v>
+        <v>711.2043876031636</v>
       </c>
       <c r="D49">
-        <v>1038.748345365296</v>
+        <v>1042.036387603164</v>
       </c>
       <c r="E49">
-        <v>27.57300000000004</v>
+        <v>35.13200000000001</v>
       </c>
       <c r="F49">
-        <v>355.273</v>
+        <v>362.832</v>
       </c>
       <c r="G49">
         <v>32</v>
@@ -5293,28 +5293,28 @@
         <v>104.4</v>
       </c>
       <c r="M49">
-        <v>19.6465969</v>
+        <v>20.0646096</v>
       </c>
       <c r="N49">
-        <v>84.7534031</v>
+        <v>84.33539040000001</v>
       </c>
       <c r="O49">
-        <v>20.340816744</v>
+        <v>20.240493696</v>
       </c>
       <c r="P49">
-        <v>64.41258635600001</v>
+        <v>64.09489670400001</v>
       </c>
       <c r="Q49">
-        <v>150.012586356</v>
+        <v>149.694896704</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2273049441568682</v>
+        <v>0.2302949853746844</v>
       </c>
       <c r="T49">
-        <v>0.8918013440915066</v>
+        <v>0.9064925294436418</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.313897390545026</v>
+        <v>5.203191194908672</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1399268323948359</v>
+        <v>0.1396288843865316</v>
       </c>
       <c r="C50">
-        <v>711.2043876031636</v>
+        <v>706.9543118038176</v>
       </c>
       <c r="D50">
-        <v>1042.036387603164</v>
+        <v>1045.345311803818</v>
       </c>
       <c r="E50">
-        <v>35.13200000000001</v>
+        <v>42.69099999999997</v>
       </c>
       <c r="F50">
-        <v>362.832</v>
+        <v>370.391</v>
       </c>
       <c r="G50">
         <v>32</v>
@@ -5375,28 +5375,28 @@
         <v>104.4</v>
       </c>
       <c r="M50">
-        <v>20.0646096</v>
+        <v>20.4826223</v>
       </c>
       <c r="N50">
-        <v>84.33539040000001</v>
+        <v>83.9173777</v>
       </c>
       <c r="O50">
-        <v>20.240493696</v>
+        <v>20.140170648</v>
       </c>
       <c r="P50">
-        <v>64.09489670400001</v>
+        <v>63.777207052</v>
       </c>
       <c r="Q50">
-        <v>149.694896704</v>
+        <v>149.377207052</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2302949853746844</v>
+        <v>0.2334022831108463</v>
       </c>
       <c r="T50">
-        <v>0.9064925294436418</v>
+        <v>0.9217598397115468</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.203191194908672</v>
+        <v>5.097003619502372</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1396288843865316</v>
+        <v>0.1393309363782274</v>
       </c>
       <c r="C51">
-        <v>706.9543118038176</v>
+        <v>702.7253175292242</v>
       </c>
       <c r="D51">
-        <v>1045.345311803818</v>
+        <v>1048.675317529224</v>
       </c>
       <c r="E51">
-        <v>42.69099999999997</v>
+        <v>50.25</v>
       </c>
       <c r="F51">
-        <v>370.391</v>
+        <v>377.95</v>
       </c>
       <c r="G51">
         <v>32</v>
@@ -5457,28 +5457,28 @@
         <v>104.4</v>
       </c>
       <c r="M51">
-        <v>20.4826223</v>
+        <v>20.900635</v>
       </c>
       <c r="N51">
-        <v>83.9173777</v>
+        <v>83.49936500000001</v>
       </c>
       <c r="O51">
-        <v>20.140170648</v>
+        <v>20.0398476</v>
       </c>
       <c r="P51">
-        <v>63.777207052</v>
+        <v>63.45951740000001</v>
       </c>
       <c r="Q51">
-        <v>149.377207052</v>
+        <v>149.0595174</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2334022831108463</v>
+        <v>0.2366338727564547</v>
       </c>
       <c r="T51">
-        <v>0.9217598397115468</v>
+        <v>0.9376378423901685</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.097003619502372</v>
+        <v>4.995063547112325</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1393309363782274</v>
+        <v>0.1390329883699231</v>
       </c>
       <c r="C52">
-        <v>702.7253175292242</v>
+        <v>698.5176068923402</v>
       </c>
       <c r="D52">
-        <v>1048.675317529224</v>
+        <v>1052.02660689234</v>
       </c>
       <c r="E52">
-        <v>50.25</v>
+        <v>57.80900000000003</v>
       </c>
       <c r="F52">
-        <v>377.95</v>
+        <v>385.509</v>
       </c>
       <c r="G52">
         <v>32</v>
@@ -5539,28 +5539,28 @@
         <v>104.4</v>
       </c>
       <c r="M52">
-        <v>20.900635</v>
+        <v>21.3186477</v>
       </c>
       <c r="N52">
-        <v>83.49936500000001</v>
+        <v>83.08135230000001</v>
       </c>
       <c r="O52">
-        <v>20.0398476</v>
+        <v>19.939524552</v>
       </c>
       <c r="P52">
-        <v>63.45951740000001</v>
+        <v>63.141827748</v>
       </c>
       <c r="Q52">
-        <v>149.0595174</v>
+        <v>148.741827748</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2366338727564547</v>
+        <v>0.2399973640202513</v>
       </c>
       <c r="T52">
-        <v>0.9376378423901685</v>
+        <v>0.9541639268107744</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.995063547112325</v>
+        <v>4.897121124619925</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1390329883699231</v>
+        <v>0.1387350403616188</v>
       </c>
       <c r="C53">
-        <v>698.5176068923402</v>
+        <v>694.3313845980044</v>
       </c>
       <c r="D53">
-        <v>1052.02660689234</v>
+        <v>1055.399384598004</v>
       </c>
       <c r="E53">
-        <v>57.80900000000003</v>
+        <v>65.36799999999999</v>
       </c>
       <c r="F53">
-        <v>385.509</v>
+        <v>393.068</v>
       </c>
       <c r="G53">
         <v>32</v>
@@ -5621,28 +5621,28 @@
         <v>104.4</v>
       </c>
       <c r="M53">
-        <v>21.3186477</v>
+        <v>21.7366604</v>
       </c>
       <c r="N53">
-        <v>83.08135230000001</v>
+        <v>82.6633396</v>
       </c>
       <c r="O53">
-        <v>19.939524552</v>
+        <v>19.839201504</v>
       </c>
       <c r="P53">
-        <v>63.141827748</v>
+        <v>62.824138096</v>
       </c>
       <c r="Q53">
-        <v>148.741827748</v>
+        <v>148.424138096</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2399973640202513</v>
+        <v>0.2435010007533726</v>
       </c>
       <c r="T53">
-        <v>0.9541639268107744</v>
+        <v>0.9713785980822389</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.897121124619925</v>
+        <v>4.802945718377236</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1387350403616188</v>
+        <v>0.1384370923533146</v>
       </c>
       <c r="C54">
-        <v>694.3313845980044</v>
+        <v>690.1668579846173</v>
       </c>
       <c r="D54">
-        <v>1055.399384598004</v>
+        <v>1058.793857984617</v>
       </c>
       <c r="E54">
-        <v>65.36799999999999</v>
+        <v>72.92700000000002</v>
       </c>
       <c r="F54">
-        <v>393.068</v>
+        <v>400.627</v>
       </c>
       <c r="G54">
         <v>32</v>
@@ -5703,28 +5703,28 @@
         <v>104.4</v>
       </c>
       <c r="M54">
-        <v>21.7366604</v>
+        <v>22.1546731</v>
       </c>
       <c r="N54">
-        <v>82.6633396</v>
+        <v>82.24532690000001</v>
       </c>
       <c r="O54">
-        <v>19.839201504</v>
+        <v>19.738878456</v>
       </c>
       <c r="P54">
-        <v>62.824138096</v>
+        <v>62.50644844400001</v>
       </c>
       <c r="Q54">
-        <v>148.424138096</v>
+        <v>148.106448444</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2435010007533726</v>
+        <v>0.2471537284113076</v>
       </c>
       <c r="T54">
-        <v>0.9713785980822389</v>
+        <v>0.9893258085567445</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.802945718377236</v>
+        <v>4.712324101049363</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1384370923533146</v>
+        <v>0.1381391443450103</v>
       </c>
       <c r="C55">
-        <v>690.1668579846173</v>
+        <v>686.0242370666305</v>
       </c>
       <c r="D55">
-        <v>1058.793857984617</v>
+        <v>1062.21023706663</v>
       </c>
       <c r="E55">
-        <v>72.92700000000002</v>
+        <v>80.48600000000005</v>
       </c>
       <c r="F55">
-        <v>400.627</v>
+        <v>408.186</v>
       </c>
       <c r="G55">
         <v>32</v>
@@ -5785,28 +5785,28 @@
         <v>104.4</v>
       </c>
       <c r="M55">
-        <v>22.1546731</v>
+        <v>22.5726858</v>
       </c>
       <c r="N55">
-        <v>82.24532690000001</v>
+        <v>81.8273142</v>
       </c>
       <c r="O55">
-        <v>19.738878456</v>
+        <v>19.638555408</v>
       </c>
       <c r="P55">
-        <v>62.50644844400001</v>
+        <v>62.188758792</v>
       </c>
       <c r="Q55">
-        <v>148.106448444</v>
+        <v>147.788758792</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2471537284113076</v>
+        <v>0.2509652703152399</v>
       </c>
       <c r="T55">
-        <v>0.9893258085567445</v>
+        <v>1.008053332530142</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.712324101049363</v>
+        <v>4.625058839918819</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1381391443450103</v>
+        <v>0.1378411963367061</v>
       </c>
       <c r="C56">
-        <v>686.0242370666305</v>
+        <v>681.9037345778605</v>
       </c>
       <c r="D56">
-        <v>1062.21023706663</v>
+        <v>1065.648734577861</v>
       </c>
       <c r="E56">
-        <v>80.48600000000005</v>
+        <v>88.04500000000002</v>
       </c>
       <c r="F56">
-        <v>408.186</v>
+        <v>415.745</v>
       </c>
       <c r="G56">
         <v>32</v>
@@ -5867,28 +5867,28 @@
         <v>104.4</v>
       </c>
       <c r="M56">
-        <v>22.5726858</v>
+        <v>22.9906985</v>
       </c>
       <c r="N56">
-        <v>81.8273142</v>
+        <v>81.4093015</v>
       </c>
       <c r="O56">
-        <v>19.638555408</v>
+        <v>19.53823236</v>
       </c>
       <c r="P56">
-        <v>62.188758792</v>
+        <v>61.87106914</v>
       </c>
       <c r="Q56">
-        <v>147.788758792</v>
+        <v>147.47106914</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2509652703152399</v>
+        <v>0.2549462140815691</v>
       </c>
       <c r="T56">
-        <v>1.008053332530142</v>
+        <v>1.027613190902356</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.625058839918819</v>
+        <v>4.540966861011205</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1378411963367061</v>
+        <v>0.1386072483284018</v>
       </c>
       <c r="C57">
-        <v>681.9037345778605</v>
+        <v>665.5486292059743</v>
       </c>
       <c r="D57">
-        <v>1065.648734577861</v>
+        <v>1056.852629205974</v>
       </c>
       <c r="E57">
-        <v>88.04500000000002</v>
+        <v>95.60400000000004</v>
       </c>
       <c r="F57">
-        <v>415.745</v>
+        <v>423.304</v>
       </c>
       <c r="G57">
         <v>32</v>
@@ -5949,45 +5949,45 @@
         <v>104.4</v>
       </c>
       <c r="M57">
-        <v>22.9906985</v>
+        <v>24.4669712</v>
       </c>
       <c r="N57">
-        <v>81.4093015</v>
+        <v>79.9330288</v>
       </c>
       <c r="O57">
-        <v>19.53823236</v>
+        <v>19.183926912</v>
       </c>
       <c r="P57">
-        <v>61.87106914</v>
+        <v>60.749101888</v>
       </c>
       <c r="Q57">
-        <v>147.47106914</v>
+        <v>146.349101888</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2549462140815691</v>
+        <v>0.2591081098372769</v>
       </c>
       <c r="T57">
-        <v>1.027613190902356</v>
+        <v>1.048062133746035</v>
       </c>
       <c r="U57">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V57">
         <v>0.24</v>
       </c>
       <c r="W57">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.540966861011205</v>
+        <v>4.266976862260744</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1386072483284018</v>
+        <v>0.1383283003200975</v>
       </c>
       <c r="C58">
-        <v>665.5486292059743</v>
+        <v>661.175756422926</v>
       </c>
       <c r="D58">
-        <v>1056.852629205974</v>
+        <v>1060.038756422926</v>
       </c>
       <c r="E58">
-        <v>95.60400000000004</v>
+        <v>103.1630000000001</v>
       </c>
       <c r="F58">
-        <v>423.304</v>
+        <v>430.8630000000001</v>
       </c>
       <c r="G58">
         <v>32</v>
@@ -6031,28 +6031,28 @@
         <v>104.4</v>
       </c>
       <c r="M58">
-        <v>24.4669712</v>
+        <v>24.90388140000001</v>
       </c>
       <c r="N58">
-        <v>79.9330288</v>
+        <v>79.4961186</v>
       </c>
       <c r="O58">
-        <v>19.183926912</v>
+        <v>19.079068464</v>
       </c>
       <c r="P58">
-        <v>60.749101888</v>
+        <v>60.417050136</v>
       </c>
       <c r="Q58">
-        <v>146.349101888</v>
+        <v>146.017050136</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2591081098372769</v>
+        <v>0.2634635821397618</v>
       </c>
       <c r="T58">
-        <v>1.048062133746035</v>
+        <v>1.069462190210351</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.266976862260744</v>
+        <v>4.192117619063186</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1383283003200975</v>
+        <v>0.1380493523117933</v>
       </c>
       <c r="C59">
-        <v>661.175756422926</v>
+        <v>656.8221523679301</v>
       </c>
       <c r="D59">
-        <v>1060.038756422926</v>
+        <v>1063.24415236793</v>
       </c>
       <c r="E59">
-        <v>103.1630000000001</v>
+        <v>110.722</v>
       </c>
       <c r="F59">
-        <v>430.8630000000001</v>
+        <v>438.422</v>
       </c>
       <c r="G59">
         <v>32</v>
@@ -6113,28 +6113,28 @@
         <v>104.4</v>
       </c>
       <c r="M59">
-        <v>24.90388140000001</v>
+        <v>25.3407916</v>
       </c>
       <c r="N59">
-        <v>79.4961186</v>
+        <v>79.0592084</v>
       </c>
       <c r="O59">
-        <v>19.079068464</v>
+        <v>18.974210016</v>
       </c>
       <c r="P59">
-        <v>60.417050136</v>
+        <v>60.084998384</v>
       </c>
       <c r="Q59">
-        <v>146.017050136</v>
+        <v>145.684998384</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2634635821397618</v>
+        <v>0.2680264578852222</v>
       </c>
       <c r="T59">
-        <v>1.069462190210351</v>
+        <v>1.09188129698249</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.192117619063186</v>
+        <v>4.11983972907934</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1380493523117933</v>
+        <v>0.1377704043034891</v>
       </c>
       <c r="C60">
-        <v>656.8221523679299</v>
+        <v>652.4879923682577</v>
       </c>
       <c r="D60">
-        <v>1063.24415236793</v>
+        <v>1066.468992368258</v>
       </c>
       <c r="E60">
-        <v>110.722</v>
+        <v>118.2809999999999</v>
       </c>
       <c r="F60">
-        <v>438.422</v>
+        <v>445.9809999999999</v>
       </c>
       <c r="G60">
         <v>32</v>
@@ -6195,28 +6195,28 @@
         <v>104.4</v>
       </c>
       <c r="M60">
-        <v>25.3407916</v>
+        <v>25.7777018</v>
       </c>
       <c r="N60">
-        <v>79.0592084</v>
+        <v>78.6222982</v>
       </c>
       <c r="O60">
-        <v>18.974210016</v>
+        <v>18.869351568</v>
       </c>
       <c r="P60">
-        <v>60.084998384</v>
+        <v>59.752946632</v>
       </c>
       <c r="Q60">
-        <v>145.684998384</v>
+        <v>145.352946632</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2680264578852222</v>
+        <v>0.2728119129353391</v>
       </c>
       <c r="T60">
-        <v>1.09188129698249</v>
+        <v>1.115394018719125</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.11983972907934</v>
+        <v>4.050011937061045</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1377704043034891</v>
+        <v>0.1390874562951848</v>
       </c>
       <c r="C61">
-        <v>652.4879923682577</v>
+        <v>629.8723581082791</v>
       </c>
       <c r="D61">
-        <v>1066.468992368258</v>
+        <v>1051.412358108279</v>
       </c>
       <c r="E61">
-        <v>118.2809999999999</v>
+        <v>125.84</v>
       </c>
       <c r="F61">
-        <v>445.9809999999999</v>
+        <v>453.54</v>
       </c>
       <c r="G61">
         <v>32</v>
@@ -6277,45 +6277,45 @@
         <v>104.4</v>
       </c>
       <c r="M61">
-        <v>25.7777018</v>
+        <v>27.802002</v>
       </c>
       <c r="N61">
-        <v>78.6222982</v>
+        <v>76.597998</v>
       </c>
       <c r="O61">
-        <v>18.869351568</v>
+        <v>18.38351952</v>
       </c>
       <c r="P61">
-        <v>59.752946632</v>
+        <v>58.21447848</v>
       </c>
       <c r="Q61">
-        <v>145.352946632</v>
+        <v>143.81447848</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2728119129353391</v>
+        <v>0.2778366407379619</v>
       </c>
       <c r="T61">
-        <v>1.115394018719125</v>
+        <v>1.140082376542591</v>
       </c>
       <c r="U61">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V61">
         <v>0.24</v>
       </c>
       <c r="W61">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.050011937061045</v>
+        <v>3.75512526040391</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1390874562951848</v>
+        <v>0.1388351082868805</v>
       </c>
       <c r="C62">
-        <v>629.8723581082791</v>
+        <v>625.1652042485225</v>
       </c>
       <c r="D62">
-        <v>1051.412358108279</v>
+        <v>1054.264204248522</v>
       </c>
       <c r="E62">
-        <v>125.84</v>
+        <v>133.399</v>
       </c>
       <c r="F62">
-        <v>453.54</v>
+        <v>461.099</v>
       </c>
       <c r="G62">
         <v>32</v>
@@ -6359,28 +6359,28 @@
         <v>104.4</v>
       </c>
       <c r="M62">
-        <v>27.802002</v>
+        <v>28.2653687</v>
       </c>
       <c r="N62">
-        <v>76.597998</v>
+        <v>76.13463130000001</v>
       </c>
       <c r="O62">
-        <v>18.38351952</v>
+        <v>18.272311512</v>
       </c>
       <c r="P62">
-        <v>58.21447848</v>
+        <v>57.86231978800001</v>
       </c>
       <c r="Q62">
-        <v>143.81447848</v>
+        <v>143.462319788</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2778366407379619</v>
+        <v>0.2831190468894373</v>
       </c>
       <c r="T62">
-        <v>1.140082376542591</v>
+        <v>1.16603680399803</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.75512526040391</v>
+        <v>3.693565829905485</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1388351082868805</v>
+        <v>0.1385827602785763</v>
       </c>
       <c r="C63">
-        <v>625.1652042485225</v>
+        <v>620.4735631346975</v>
       </c>
       <c r="D63">
-        <v>1054.264204248522</v>
+        <v>1057.131563134697</v>
       </c>
       <c r="E63">
-        <v>133.399</v>
+        <v>140.958</v>
       </c>
       <c r="F63">
-        <v>461.099</v>
+        <v>468.658</v>
       </c>
       <c r="G63">
         <v>32</v>
@@ -6441,28 +6441,28 @@
         <v>104.4</v>
       </c>
       <c r="M63">
-        <v>28.2653687</v>
+        <v>28.7287354</v>
       </c>
       <c r="N63">
-        <v>76.13463130000001</v>
+        <v>75.6712646</v>
       </c>
       <c r="O63">
-        <v>18.272311512</v>
+        <v>18.161103504</v>
       </c>
       <c r="P63">
-        <v>57.86231978800001</v>
+        <v>57.510161096</v>
       </c>
       <c r="Q63">
-        <v>143.462319788</v>
+        <v>143.110161096</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2831190468894373</v>
+        <v>0.288679474417306</v>
       </c>
       <c r="T63">
-        <v>1.16603680399803</v>
+        <v>1.193357253951123</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.693565829905485</v>
+        <v>3.633992187487654</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1385827602785763</v>
+        <v>0.138330412270272</v>
       </c>
       <c r="C64">
-        <v>620.4735631346975</v>
+        <v>615.7975616854161</v>
       </c>
       <c r="D64">
-        <v>1057.131563134697</v>
+        <v>1060.014561685416</v>
       </c>
       <c r="E64">
-        <v>140.958</v>
+        <v>148.517</v>
       </c>
       <c r="F64">
-        <v>468.658</v>
+        <v>476.217</v>
       </c>
       <c r="G64">
         <v>32</v>
@@ -6523,28 +6523,28 @@
         <v>104.4</v>
       </c>
       <c r="M64">
-        <v>28.7287354</v>
+        <v>29.1921021</v>
       </c>
       <c r="N64">
-        <v>75.6712646</v>
+        <v>75.20789790000001</v>
       </c>
       <c r="O64">
-        <v>18.161103504</v>
+        <v>18.049895496</v>
       </c>
       <c r="P64">
-        <v>57.510161096</v>
+        <v>57.158002404</v>
       </c>
       <c r="Q64">
-        <v>143.110161096</v>
+        <v>142.758002404</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.288679474417306</v>
+        <v>0.2945404655953298</v>
       </c>
       <c r="T64">
-        <v>1.193357253951123</v>
+        <v>1.222154484982762</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.633992187487654</v>
+        <v>3.576309771813247</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.138330412270272</v>
+        <v>0.1380780642619678</v>
       </c>
       <c r="C65">
-        <v>615.7975616854161</v>
+        <v>611.1373282076031</v>
       </c>
       <c r="D65">
-        <v>1060.014561685416</v>
+        <v>1062.913328207603</v>
       </c>
       <c r="E65">
-        <v>148.517</v>
+        <v>156.076</v>
       </c>
       <c r="F65">
-        <v>476.217</v>
+        <v>483.776</v>
       </c>
       <c r="G65">
         <v>32</v>
@@ -6605,28 +6605,28 @@
         <v>104.4</v>
       </c>
       <c r="M65">
-        <v>29.1921021</v>
+        <v>29.6554688</v>
       </c>
       <c r="N65">
-        <v>75.20789790000001</v>
+        <v>74.74453120000001</v>
       </c>
       <c r="O65">
-        <v>18.049895496</v>
+        <v>17.938687488</v>
       </c>
       <c r="P65">
-        <v>57.158002404</v>
+        <v>56.80584371200001</v>
       </c>
       <c r="Q65">
-        <v>142.758002404</v>
+        <v>142.405843712</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2945404655953298</v>
+        <v>0.3007270673943549</v>
       </c>
       <c r="T65">
-        <v>1.222154484982762</v>
+        <v>1.252551562182826</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.576309771813247</v>
+        <v>3.520429931628665</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1380780642619678</v>
+        <v>0.1392089162536635</v>
       </c>
       <c r="C66">
-        <v>611.1373282076031</v>
+        <v>590.710202739373</v>
       </c>
       <c r="D66">
-        <v>1062.913328207603</v>
+        <v>1050.045202739373</v>
       </c>
       <c r="E66">
-        <v>156.076</v>
+        <v>163.635</v>
       </c>
       <c r="F66">
-        <v>483.776</v>
+        <v>491.335</v>
       </c>
       <c r="G66">
         <v>32</v>
@@ -6687,45 +6687,45 @@
         <v>104.4</v>
       </c>
       <c r="M66">
-        <v>29.6554688</v>
+        <v>31.4945735</v>
       </c>
       <c r="N66">
-        <v>74.74453120000001</v>
+        <v>72.9054265</v>
       </c>
       <c r="O66">
-        <v>17.938687488</v>
+        <v>17.49730236</v>
       </c>
       <c r="P66">
-        <v>56.80584371200001</v>
+        <v>55.40812414000001</v>
       </c>
       <c r="Q66">
-        <v>142.405843712</v>
+        <v>141.00812414</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3007270673943549</v>
+        <v>0.3072671892961815</v>
       </c>
       <c r="T66">
-        <v>1.252551562182826</v>
+        <v>1.284685615222893</v>
       </c>
       <c r="U66">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V66">
         <v>0.24</v>
       </c>
       <c r="W66">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.520429931628665</v>
+        <v>3.314856764134304</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1392089162536635</v>
+        <v>0.1389778482453593</v>
       </c>
       <c r="C67">
-        <v>590.710202739373</v>
+        <v>585.7551677181254</v>
       </c>
       <c r="D67">
-        <v>1050.045202739373</v>
+        <v>1052.649167718125</v>
       </c>
       <c r="E67">
-        <v>163.635</v>
+        <v>171.194</v>
       </c>
       <c r="F67">
-        <v>491.335</v>
+        <v>498.894</v>
       </c>
       <c r="G67">
         <v>32</v>
@@ -6769,28 +6769,28 @@
         <v>104.4</v>
       </c>
       <c r="M67">
-        <v>31.4945735</v>
+        <v>31.9791054</v>
       </c>
       <c r="N67">
-        <v>72.9054265</v>
+        <v>72.4208946</v>
       </c>
       <c r="O67">
-        <v>17.49730236</v>
+        <v>17.381014704</v>
       </c>
       <c r="P67">
-        <v>55.40812414000001</v>
+        <v>55.039879896</v>
       </c>
       <c r="Q67">
-        <v>141.00812414</v>
+        <v>140.639879896</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3072671892961815</v>
+        <v>0.3141920242510567</v>
       </c>
       <c r="T67">
-        <v>1.284685615222893</v>
+        <v>1.318709906677082</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.314856764134304</v>
+        <v>3.26463166164742</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1389778482453593</v>
+        <v>0.138746780237055</v>
       </c>
       <c r="C68">
-        <v>585.7551677181254</v>
+        <v>580.8130797403321</v>
       </c>
       <c r="D68">
-        <v>1052.649167718125</v>
+        <v>1055.266079740332</v>
       </c>
       <c r="E68">
-        <v>171.194</v>
+        <v>178.753</v>
       </c>
       <c r="F68">
-        <v>498.894</v>
+        <v>506.453</v>
       </c>
       <c r="G68">
         <v>32</v>
@@ -6851,28 +6851,28 @@
         <v>104.4</v>
       </c>
       <c r="M68">
-        <v>31.9791054</v>
+        <v>32.4636373</v>
       </c>
       <c r="N68">
-        <v>72.4208946</v>
+        <v>71.9363627</v>
       </c>
       <c r="O68">
-        <v>17.381014704</v>
+        <v>17.264727048</v>
       </c>
       <c r="P68">
-        <v>55.039879896</v>
+        <v>54.67163565200001</v>
       </c>
       <c r="Q68">
-        <v>140.639879896</v>
+        <v>140.271635652</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3141920242510567</v>
+        <v>0.321536546172894</v>
       </c>
       <c r="T68">
-        <v>1.318709906677082</v>
+        <v>1.354796276401222</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.26463166164742</v>
+        <v>3.21590581595119</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.138746780237055</v>
+        <v>0.1385157122287507</v>
       </c>
       <c r="C69">
-        <v>580.8130797403321</v>
+        <v>575.884035606659</v>
       </c>
       <c r="D69">
-        <v>1055.266079740332</v>
+        <v>1057.896035606659</v>
       </c>
       <c r="E69">
-        <v>178.753</v>
+        <v>186.3120000000001</v>
       </c>
       <c r="F69">
-        <v>506.453</v>
+        <v>514.0120000000001</v>
       </c>
       <c r="G69">
         <v>32</v>
@@ -6933,28 +6933,28 @@
         <v>104.4</v>
       </c>
       <c r="M69">
-        <v>32.4636373</v>
+        <v>32.9481692</v>
       </c>
       <c r="N69">
-        <v>71.9363627</v>
+        <v>71.45183080000001</v>
       </c>
       <c r="O69">
-        <v>17.264727048</v>
+        <v>17.148439392</v>
       </c>
       <c r="P69">
-        <v>54.67163565200001</v>
+        <v>54.30339140800001</v>
       </c>
       <c r="Q69">
-        <v>140.271635652</v>
+        <v>139.903391408</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.321536546172894</v>
+        <v>0.3293401007148461</v>
       </c>
       <c r="T69">
-        <v>1.354796276401222</v>
+        <v>1.39313804423312</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.21590581595119</v>
+        <v>3.168613083363673</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1385157122287507</v>
+        <v>0.1382846442204465</v>
       </c>
       <c r="C70">
-        <v>575.884035606659</v>
+        <v>570.968133085176</v>
       </c>
       <c r="D70">
-        <v>1057.896035606659</v>
+        <v>1060.539133085176</v>
       </c>
       <c r="E70">
-        <v>186.3120000000001</v>
+        <v>193.871</v>
       </c>
       <c r="F70">
-        <v>514.0120000000001</v>
+        <v>521.571</v>
       </c>
       <c r="G70">
         <v>32</v>
@@ -7015,28 +7015,28 @@
         <v>104.4</v>
       </c>
       <c r="M70">
-        <v>32.9481692</v>
+        <v>33.4327011</v>
       </c>
       <c r="N70">
-        <v>71.45183080000001</v>
+        <v>70.9672989</v>
       </c>
       <c r="O70">
-        <v>17.148439392</v>
+        <v>17.032151736</v>
       </c>
       <c r="P70">
-        <v>54.30339140800001</v>
+        <v>53.935147164</v>
       </c>
       <c r="Q70">
-        <v>139.903391408</v>
+        <v>139.535147164</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3293401007148461</v>
+        <v>0.3376471103885371</v>
       </c>
       <c r="T70">
-        <v>1.39313804423312</v>
+        <v>1.433953474505786</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.168613083363673</v>
+        <v>3.122691154619272</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1382846442204465</v>
+        <v>0.1380535762121422</v>
       </c>
       <c r="C71">
-        <v>570.968133085176</v>
+        <v>566.0654709234749</v>
       </c>
       <c r="D71">
-        <v>1060.539133085176</v>
+        <v>1063.195470923475</v>
       </c>
       <c r="E71">
-        <v>193.871</v>
+        <v>201.43</v>
       </c>
       <c r="F71">
-        <v>521.571</v>
+        <v>529.13</v>
       </c>
       <c r="G71">
         <v>32</v>
@@ -7097,28 +7097,28 @@
         <v>104.4</v>
       </c>
       <c r="M71">
-        <v>33.4327011</v>
+        <v>33.917233</v>
       </c>
       <c r="N71">
-        <v>70.9672989</v>
+        <v>70.482767</v>
       </c>
       <c r="O71">
-        <v>17.032151736</v>
+        <v>16.91586408</v>
       </c>
       <c r="P71">
-        <v>53.935147164</v>
+        <v>53.56690292</v>
       </c>
       <c r="Q71">
-        <v>139.535147164</v>
+        <v>139.16690292</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3376471103885371</v>
+        <v>0.3465079207071409</v>
       </c>
       <c r="T71">
-        <v>1.433953474505786</v>
+        <v>1.477489933463296</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.122691154619272</v>
+        <v>3.078081280981853</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1380535762121422</v>
+        <v>0.137822508203838</v>
       </c>
       <c r="C72">
-        <v>566.0654709234749</v>
+        <v>561.1761488609659</v>
       </c>
       <c r="D72">
-        <v>1063.195470923475</v>
+        <v>1065.865148860966</v>
       </c>
       <c r="E72">
-        <v>201.43</v>
+        <v>208.9890000000001</v>
       </c>
       <c r="F72">
-        <v>529.13</v>
+        <v>536.6890000000001</v>
       </c>
       <c r="G72">
         <v>32</v>
@@ -7179,28 +7179,28 @@
         <v>104.4</v>
       </c>
       <c r="M72">
-        <v>33.917233</v>
+        <v>34.40176490000001</v>
       </c>
       <c r="N72">
-        <v>70.482767</v>
+        <v>69.99823509999999</v>
       </c>
       <c r="O72">
-        <v>16.91586408</v>
+        <v>16.799576424</v>
       </c>
       <c r="P72">
-        <v>53.56690292</v>
+        <v>53.19865867599999</v>
       </c>
       <c r="Q72">
-        <v>139.16690292</v>
+        <v>138.798658676</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3465079207071409</v>
+        <v>0.3559798213925449</v>
       </c>
       <c r="T72">
-        <v>1.477489933463296</v>
+        <v>1.524028906831669</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.078081280981853</v>
+        <v>3.034728023503235</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.137822508203838</v>
+        <v>0.1418596001955337</v>
       </c>
       <c r="C73">
-        <v>561.176148860966</v>
+        <v>508.8220877953853</v>
       </c>
       <c r="D73">
-        <v>1065.865148860966</v>
+        <v>1021.070087795385</v>
       </c>
       <c r="E73">
-        <v>208.989</v>
+        <v>216.5479999999999</v>
       </c>
       <c r="F73">
-        <v>536.689</v>
+        <v>544.2479999999999</v>
       </c>
       <c r="G73">
         <v>32</v>
@@ -7261,45 +7261,45 @@
         <v>104.4</v>
       </c>
       <c r="M73">
-        <v>34.4017649</v>
+        <v>39.1314312</v>
       </c>
       <c r="N73">
-        <v>69.9982351</v>
+        <v>65.2685688</v>
       </c>
       <c r="O73">
-        <v>16.799576424</v>
+        <v>15.664456512</v>
       </c>
       <c r="P73">
-        <v>53.198658676</v>
+        <v>49.604112288</v>
       </c>
       <c r="Q73">
-        <v>138.798658676</v>
+        <v>135.204112288</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3559798213925447</v>
+        <v>0.3661282864126204</v>
       </c>
       <c r="T73">
-        <v>1.524028906831669</v>
+        <v>1.573892092583497</v>
       </c>
       <c r="U73">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V73">
         <v>0.24</v>
       </c>
       <c r="W73">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.034728023503236</v>
+        <v>2.667932063777928</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1418596001955337</v>
+        <v>0.1416878121872295</v>
       </c>
       <c r="C74">
-        <v>508.8220877953853</v>
+        <v>503.0923880236448</v>
       </c>
       <c r="D74">
-        <v>1021.070087795385</v>
+        <v>1022.899388023645</v>
       </c>
       <c r="E74">
-        <v>216.5479999999999</v>
+        <v>224.107</v>
       </c>
       <c r="F74">
-        <v>544.2479999999999</v>
+        <v>551.807</v>
       </c>
       <c r="G74">
         <v>32</v>
@@ -7343,28 +7343,28 @@
         <v>104.4</v>
       </c>
       <c r="M74">
-        <v>39.1314312</v>
+        <v>39.6749233</v>
       </c>
       <c r="N74">
-        <v>65.2685688</v>
+        <v>64.7250767</v>
       </c>
       <c r="O74">
-        <v>15.664456512</v>
+        <v>15.534018408</v>
       </c>
       <c r="P74">
-        <v>49.604112288</v>
+        <v>49.191058292</v>
       </c>
       <c r="Q74">
-        <v>135.204112288</v>
+        <v>134.791058292</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3661282864126204</v>
+        <v>0.3770284895823313</v>
       </c>
       <c r="T74">
-        <v>1.573892092583497</v>
+        <v>1.627448847650275</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.667932063777928</v>
+        <v>2.631385049205627</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1416878121872295</v>
+        <v>0.1415160241789252</v>
       </c>
       <c r="C75">
-        <v>503.0923880236448</v>
+        <v>497.3692545890569</v>
       </c>
       <c r="D75">
-        <v>1022.899388023645</v>
+        <v>1024.735254589057</v>
       </c>
       <c r="E75">
-        <v>224.107</v>
+        <v>231.666</v>
       </c>
       <c r="F75">
-        <v>551.807</v>
+        <v>559.366</v>
       </c>
       <c r="G75">
         <v>32</v>
@@ -7425,28 +7425,28 @@
         <v>104.4</v>
       </c>
       <c r="M75">
-        <v>39.6749233</v>
+        <v>40.2184154</v>
       </c>
       <c r="N75">
-        <v>64.7250767</v>
+        <v>64.18158460000001</v>
       </c>
       <c r="O75">
-        <v>15.534018408</v>
+        <v>15.403580304</v>
       </c>
       <c r="P75">
-        <v>49.191058292</v>
+        <v>48.77800429600001</v>
       </c>
       <c r="Q75">
-        <v>134.791058292</v>
+        <v>134.378004296</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3770284895823313</v>
+        <v>0.3887671699189431</v>
       </c>
       <c r="T75">
-        <v>1.627448847650275</v>
+        <v>1.685125353106806</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.631385049205627</v>
+        <v>2.59582579178393</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1415160241789252</v>
+        <v>0.141344236170621</v>
       </c>
       <c r="C76">
-        <v>497.3692545890569</v>
+        <v>491.6527229103338</v>
       </c>
       <c r="D76">
-        <v>1024.735254589057</v>
+        <v>1026.577722910334</v>
       </c>
       <c r="E76">
-        <v>231.666</v>
+        <v>239.225</v>
       </c>
       <c r="F76">
-        <v>559.366</v>
+        <v>566.925</v>
       </c>
       <c r="G76">
         <v>32</v>
@@ -7507,28 +7507,28 @@
         <v>104.4</v>
       </c>
       <c r="M76">
-        <v>40.2184154</v>
+        <v>40.7619075</v>
       </c>
       <c r="N76">
-        <v>64.18158460000001</v>
+        <v>63.63809250000001</v>
       </c>
       <c r="O76">
-        <v>15.403580304</v>
+        <v>15.2731422</v>
       </c>
       <c r="P76">
-        <v>48.77800429600001</v>
+        <v>48.3649503</v>
       </c>
       <c r="Q76">
-        <v>134.378004296</v>
+        <v>133.9649503</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3887671699189431</v>
+        <v>0.4014449446824838</v>
       </c>
       <c r="T76">
-        <v>1.685125353106806</v>
+        <v>1.747415978999859</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.59582579178393</v>
+        <v>2.561214781226811</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.141344236170621</v>
+        <v>0.1411724481623167</v>
       </c>
       <c r="C77">
-        <v>491.6527229103338</v>
+        <v>485.9428286613801</v>
       </c>
       <c r="D77">
-        <v>1026.577722910334</v>
+        <v>1028.42682866138</v>
       </c>
       <c r="E77">
-        <v>239.225</v>
+        <v>246.784</v>
       </c>
       <c r="F77">
-        <v>566.925</v>
+        <v>574.484</v>
       </c>
       <c r="G77">
         <v>32</v>
@@ -7589,28 +7589,28 @@
         <v>104.4</v>
       </c>
       <c r="M77">
-        <v>40.7619075</v>
+        <v>41.30539960000001</v>
       </c>
       <c r="N77">
-        <v>63.63809250000001</v>
+        <v>63.0946004</v>
       </c>
       <c r="O77">
-        <v>15.2731422</v>
+        <v>15.142704096</v>
       </c>
       <c r="P77">
-        <v>48.3649503</v>
+        <v>47.951896304</v>
       </c>
       <c r="Q77">
-        <v>133.9649503</v>
+        <v>133.551896304</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4014449446824838</v>
+        <v>0.4151792006763196</v>
       </c>
       <c r="T77">
-        <v>1.747415978999859</v>
+        <v>1.814897490384</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.561214781226811</v>
+        <v>2.527514586736984</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1411724481623167</v>
+        <v>0.1432829401540124</v>
       </c>
       <c r="C78">
-        <v>485.9428286613801</v>
+        <v>456.1185319591494</v>
       </c>
       <c r="D78">
-        <v>1028.42682866138</v>
+        <v>1006.161531959149</v>
       </c>
       <c r="E78">
-        <v>246.784</v>
+        <v>254.343</v>
       </c>
       <c r="F78">
-        <v>574.484</v>
+        <v>582.043</v>
       </c>
       <c r="G78">
         <v>32</v>
@@ -7671,45 +7671,45 @@
         <v>104.4</v>
       </c>
       <c r="M78">
-        <v>41.30539960000001</v>
+        <v>44.11885940000001</v>
       </c>
       <c r="N78">
-        <v>63.0946004</v>
+        <v>60.2811406</v>
       </c>
       <c r="O78">
-        <v>15.142704096</v>
+        <v>14.467473744</v>
       </c>
       <c r="P78">
-        <v>47.951896304</v>
+        <v>45.813666856</v>
       </c>
       <c r="Q78">
-        <v>133.551896304</v>
+        <v>131.413666856</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4151792006763196</v>
+        <v>0.4301077398000541</v>
       </c>
       <c r="T78">
-        <v>1.814897490384</v>
+        <v>1.888246959279806</v>
       </c>
       <c r="U78">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0.24</v>
       </c>
       <c r="W78">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.527514586736984</v>
+        <v>2.366334973745944</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1432829401540124</v>
+        <v>0.1431407921457082</v>
       </c>
       <c r="C79">
-        <v>456.1185319591494</v>
+        <v>450.028842560056</v>
       </c>
       <c r="D79">
-        <v>1006.161531959149</v>
+        <v>1007.630842560056</v>
       </c>
       <c r="E79">
-        <v>254.343</v>
+        <v>261.902</v>
       </c>
       <c r="F79">
-        <v>582.043</v>
+        <v>589.602</v>
       </c>
       <c r="G79">
         <v>32</v>
@@ -7753,28 +7753,28 @@
         <v>104.4</v>
       </c>
       <c r="M79">
-        <v>44.11885940000001</v>
+        <v>44.6918316</v>
       </c>
       <c r="N79">
-        <v>60.2811406</v>
+        <v>59.70816840000001</v>
       </c>
       <c r="O79">
-        <v>14.467473744</v>
+        <v>14.329960416</v>
       </c>
       <c r="P79">
-        <v>45.813666856</v>
+        <v>45.37820798400001</v>
       </c>
       <c r="Q79">
-        <v>131.413666856</v>
+        <v>130.978207984</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4301077398000541</v>
+        <v>0.4463934188441281</v>
       </c>
       <c r="T79">
-        <v>1.888246959279806</v>
+        <v>1.968264561711593</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.366334973745944</v>
+        <v>2.335997345877407</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1431407921457082</v>
+        <v>0.1429986441374039</v>
       </c>
       <c r="C80">
-        <v>450.028842560056</v>
+        <v>443.9434507430401</v>
       </c>
       <c r="D80">
-        <v>1007.630842560056</v>
+        <v>1009.10445074304</v>
       </c>
       <c r="E80">
-        <v>261.902</v>
+        <v>269.4610000000001</v>
       </c>
       <c r="F80">
-        <v>589.602</v>
+        <v>597.1610000000001</v>
       </c>
       <c r="G80">
         <v>32</v>
@@ -7835,28 +7835,28 @@
         <v>104.4</v>
       </c>
       <c r="M80">
-        <v>44.6918316</v>
+        <v>45.26480380000001</v>
       </c>
       <c r="N80">
-        <v>59.70816840000001</v>
+        <v>59.1351962</v>
       </c>
       <c r="O80">
-        <v>14.329960416</v>
+        <v>14.192447088</v>
       </c>
       <c r="P80">
-        <v>45.37820798400001</v>
+        <v>44.942749112</v>
       </c>
       <c r="Q80">
-        <v>130.978207984</v>
+        <v>130.542749112</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4463934188441281</v>
+        <v>0.4642301149400188</v>
       </c>
       <c r="T80">
-        <v>1.968264561711593</v>
+        <v>2.055902888184504</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.335997345877407</v>
+        <v>2.30642775922073</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1429986441374039</v>
+        <v>0.1428564961290997</v>
       </c>
       <c r="C81">
-        <v>443.9434507430401</v>
+        <v>437.8623753906938</v>
       </c>
       <c r="D81">
-        <v>1009.10445074304</v>
+        <v>1010.582375390694</v>
       </c>
       <c r="E81">
-        <v>269.4610000000001</v>
+        <v>277.02</v>
       </c>
       <c r="F81">
-        <v>597.1610000000001</v>
+        <v>604.72</v>
       </c>
       <c r="G81">
         <v>32</v>
@@ -7917,28 +7917,28 @@
         <v>104.4</v>
       </c>
       <c r="M81">
-        <v>45.26480380000001</v>
+        <v>45.83777600000001</v>
       </c>
       <c r="N81">
-        <v>59.1351962</v>
+        <v>58.562224</v>
       </c>
       <c r="O81">
-        <v>14.192447088</v>
+        <v>14.05493376</v>
       </c>
       <c r="P81">
-        <v>44.942749112</v>
+        <v>44.50729024</v>
       </c>
       <c r="Q81">
-        <v>130.542749112</v>
+        <v>130.10729024</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4642301149400188</v>
+        <v>0.4838504806454984</v>
       </c>
       <c r="T81">
-        <v>2.055902888184504</v>
+        <v>2.152305047304705</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.30642775922073</v>
+        <v>2.277597412230471</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1428564961290997</v>
+        <v>0.1427143481207954</v>
       </c>
       <c r="C82">
-        <v>437.8623753906938</v>
+        <v>431.7856354963917</v>
       </c>
       <c r="D82">
-        <v>1010.582375390694</v>
+        <v>1012.064635496392</v>
       </c>
       <c r="E82">
-        <v>277.02</v>
+        <v>284.579</v>
       </c>
       <c r="F82">
-        <v>604.72</v>
+        <v>612.279</v>
       </c>
       <c r="G82">
         <v>32</v>
@@ -7999,28 +7999,28 @@
         <v>104.4</v>
       </c>
       <c r="M82">
-        <v>45.83777600000001</v>
+        <v>46.4107482</v>
       </c>
       <c r="N82">
-        <v>58.562224</v>
+        <v>57.98925180000001</v>
       </c>
       <c r="O82">
-        <v>14.05493376</v>
+        <v>13.917420432</v>
       </c>
       <c r="P82">
-        <v>44.50729024</v>
+        <v>44.07183136800001</v>
       </c>
       <c r="Q82">
-        <v>130.10729024</v>
+        <v>129.671831368</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4838504806454984</v>
+        <v>0.5055361480041864</v>
       </c>
       <c r="T82">
-        <v>2.152305047304705</v>
+        <v>2.25885480212177</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.277597412230471</v>
+        <v>2.249478925659725</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1427143481207954</v>
+        <v>0.1425722001124911</v>
       </c>
       <c r="C83">
-        <v>431.7856354963917</v>
+        <v>425.7132501651064</v>
       </c>
       <c r="D83">
-        <v>1012.064635496392</v>
+        <v>1013.551250165106</v>
       </c>
       <c r="E83">
-        <v>284.579</v>
+        <v>292.1380000000001</v>
       </c>
       <c r="F83">
-        <v>612.279</v>
+        <v>619.8380000000001</v>
       </c>
       <c r="G83">
         <v>32</v>
@@ -8081,28 +8081,28 @@
         <v>104.4</v>
       </c>
       <c r="M83">
-        <v>46.4107482</v>
+        <v>46.98372040000001</v>
       </c>
       <c r="N83">
-        <v>57.98925180000001</v>
+        <v>57.4162796</v>
       </c>
       <c r="O83">
-        <v>13.917420432</v>
+        <v>13.779907104</v>
       </c>
       <c r="P83">
-        <v>44.07183136800001</v>
+        <v>43.636372496</v>
       </c>
       <c r="Q83">
-        <v>129.671831368</v>
+        <v>129.236372496</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5055361480041864</v>
+        <v>0.5296313339582843</v>
       </c>
       <c r="T83">
-        <v>2.25885480212177</v>
+        <v>2.377243418585175</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.249478925659725</v>
+        <v>2.222046255834606</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1425722001124911</v>
+        <v>0.1424300521041869</v>
       </c>
       <c r="C84">
-        <v>425.7132501651064</v>
+        <v>419.6452386142265</v>
       </c>
       <c r="D84">
-        <v>1013.551250165106</v>
+        <v>1015.042238614227</v>
       </c>
       <c r="E84">
-        <v>292.1380000000001</v>
+        <v>299.6970000000001</v>
       </c>
       <c r="F84">
-        <v>619.8380000000001</v>
+        <v>627.397</v>
       </c>
       <c r="G84">
         <v>32</v>
@@ -8163,28 +8163,28 @@
         <v>104.4</v>
       </c>
       <c r="M84">
-        <v>46.98372040000001</v>
+        <v>47.55669260000001</v>
       </c>
       <c r="N84">
-        <v>57.4162796</v>
+        <v>56.8433074</v>
       </c>
       <c r="O84">
-        <v>13.779907104</v>
+        <v>13.642393776</v>
       </c>
       <c r="P84">
-        <v>43.636372496</v>
+        <v>43.200913624</v>
       </c>
       <c r="Q84">
-        <v>129.236372496</v>
+        <v>128.800913624</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5296313339582843</v>
+        <v>0.5565612476716878</v>
       </c>
       <c r="T84">
-        <v>2.377243418585175</v>
+        <v>2.509560107573687</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.222046255834606</v>
+        <v>2.195274614198044</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1424300521041869</v>
+        <v>0.1422879040958827</v>
       </c>
       <c r="C85">
-        <v>419.6452386142265</v>
+        <v>413.5816201743888</v>
       </c>
       <c r="D85">
-        <v>1015.042238614227</v>
+        <v>1016.537620174389</v>
       </c>
       <c r="E85">
-        <v>299.6970000000001</v>
+        <v>307.256</v>
       </c>
       <c r="F85">
-        <v>627.397</v>
+        <v>634.956</v>
       </c>
       <c r="G85">
         <v>32</v>
@@ -8245,28 +8245,28 @@
         <v>104.4</v>
       </c>
       <c r="M85">
-        <v>47.55669260000001</v>
+        <v>48.12966480000001</v>
       </c>
       <c r="N85">
-        <v>56.8433074</v>
+        <v>56.2703352</v>
       </c>
       <c r="O85">
-        <v>13.642393776</v>
+        <v>13.504880448</v>
       </c>
       <c r="P85">
-        <v>43.200913624</v>
+        <v>42.765454752</v>
       </c>
       <c r="Q85">
-        <v>128.800913624</v>
+        <v>128.365454752</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5565612476716878</v>
+        <v>0.5868574005992667</v>
       </c>
       <c r="T85">
-        <v>2.509560107573687</v>
+        <v>2.658416382685763</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.195274614198044</v>
+        <v>2.169140392600449</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1422879040958827</v>
+        <v>0.1421457560875784</v>
       </c>
       <c r="C86">
-        <v>413.5816201743889</v>
+        <v>407.5224142903102</v>
       </c>
       <c r="D86">
-        <v>1016.537620174389</v>
+        <v>1018.03741429031</v>
       </c>
       <c r="E86">
-        <v>307.2559999999999</v>
+        <v>314.815</v>
       </c>
       <c r="F86">
-        <v>634.9559999999999</v>
+        <v>642.515</v>
       </c>
       <c r="G86">
         <v>32</v>
@@ -8327,28 +8327,28 @@
         <v>104.4</v>
       </c>
       <c r="M86">
-        <v>48.12966479999999</v>
+        <v>48.702637</v>
       </c>
       <c r="N86">
-        <v>56.27033520000001</v>
+        <v>55.697363</v>
       </c>
       <c r="O86">
-        <v>13.504880448</v>
+        <v>13.36736712</v>
       </c>
       <c r="P86">
-        <v>42.76545475200001</v>
+        <v>42.32999588</v>
       </c>
       <c r="Q86">
-        <v>128.365454752</v>
+        <v>127.92999588</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5868574005992664</v>
+        <v>0.6211930405838558</v>
       </c>
       <c r="T86">
-        <v>2.658416382685761</v>
+        <v>2.827120161146114</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.169140392600449</v>
+        <v>2.143621093863973</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1421457560875784</v>
+        <v>0.1420036080792741</v>
       </c>
       <c r="C87">
-        <v>407.5224142903102</v>
+        <v>401.4676405216318</v>
       </c>
       <c r="D87">
-        <v>1018.03741429031</v>
+        <v>1019.541640521632</v>
       </c>
       <c r="E87">
-        <v>314.815</v>
+        <v>322.374</v>
       </c>
       <c r="F87">
-        <v>642.515</v>
+        <v>650.074</v>
       </c>
       <c r="G87">
         <v>32</v>
@@ -8409,28 +8409,28 @@
         <v>104.4</v>
       </c>
       <c r="M87">
-        <v>48.702637</v>
+        <v>49.2756092</v>
       </c>
       <c r="N87">
-        <v>55.697363</v>
+        <v>55.12439080000001</v>
       </c>
       <c r="O87">
-        <v>13.36736712</v>
+        <v>13.229853792</v>
       </c>
       <c r="P87">
-        <v>42.32999588</v>
+        <v>41.89453700800001</v>
       </c>
       <c r="Q87">
-        <v>127.92999588</v>
+        <v>127.494537008</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6211930405838558</v>
+        <v>0.6604337719948151</v>
       </c>
       <c r="T87">
-        <v>2.827120161146114</v>
+        <v>3.019924479386516</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.143621093863973</v>
+        <v>2.118695267191137</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1420036080792741</v>
+        <v>0.1418614600709699</v>
       </c>
       <c r="C88">
-        <v>401.4676405216318</v>
+        <v>395.4173185437679</v>
       </c>
       <c r="D88">
-        <v>1019.541640521632</v>
+        <v>1021.050318543768</v>
       </c>
       <c r="E88">
-        <v>322.374</v>
+        <v>329.9329999999999</v>
       </c>
       <c r="F88">
-        <v>650.074</v>
+        <v>657.6329999999999</v>
       </c>
       <c r="G88">
         <v>32</v>
@@ -8491,28 +8491,28 @@
         <v>104.4</v>
       </c>
       <c r="M88">
-        <v>49.2756092</v>
+        <v>49.8485814</v>
       </c>
       <c r="N88">
-        <v>55.12439080000001</v>
+        <v>54.55141860000001</v>
       </c>
       <c r="O88">
-        <v>13.229853792</v>
+        <v>13.092340464</v>
       </c>
       <c r="P88">
-        <v>41.89453700800001</v>
+        <v>41.459078136</v>
       </c>
       <c r="Q88">
-        <v>127.494537008</v>
+        <v>127.059078136</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6604337719948151</v>
+        <v>0.7057115390074605</v>
       </c>
       <c r="T88">
-        <v>3.019924479386516</v>
+        <v>3.242391000433135</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.118695267191137</v>
+        <v>2.094342448028019</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1418614600709699</v>
+        <v>0.1417193120626656</v>
       </c>
       <c r="C89">
-        <v>395.4173185437679</v>
+        <v>389.3714681487672</v>
       </c>
       <c r="D89">
-        <v>1021.050318543768</v>
+        <v>1022.563468148767</v>
       </c>
       <c r="E89">
-        <v>329.9329999999999</v>
+        <v>337.492</v>
       </c>
       <c r="F89">
-        <v>657.6329999999999</v>
+        <v>665.192</v>
       </c>
       <c r="G89">
         <v>32</v>
@@ -8573,28 +8573,28 @@
         <v>104.4</v>
       </c>
       <c r="M89">
-        <v>49.8485814</v>
+        <v>50.4215536</v>
       </c>
       <c r="N89">
-        <v>54.55141860000001</v>
+        <v>53.9784464</v>
       </c>
       <c r="O89">
-        <v>13.092340464</v>
+        <v>12.954827136</v>
       </c>
       <c r="P89">
-        <v>41.459078136</v>
+        <v>41.023619264</v>
       </c>
       <c r="Q89">
-        <v>127.059078136</v>
+        <v>126.623619264</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7057115390074605</v>
+        <v>0.7585356005222135</v>
       </c>
       <c r="T89">
-        <v>3.242391000433135</v>
+        <v>3.501935274987523</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.094342448028019</v>
+        <v>2.070543102027701</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1417193120626656</v>
+        <v>0.1415771640543613</v>
       </c>
       <c r="C90">
-        <v>389.3714681487672</v>
+        <v>383.3301092461752</v>
       </c>
       <c r="D90">
-        <v>1022.563468148767</v>
+        <v>1024.081109246175</v>
       </c>
       <c r="E90">
-        <v>337.492</v>
+        <v>345.051</v>
       </c>
       <c r="F90">
-        <v>665.192</v>
+        <v>672.751</v>
       </c>
       <c r="G90">
         <v>32</v>
@@ -8655,28 +8655,28 @@
         <v>104.4</v>
       </c>
       <c r="M90">
-        <v>50.4215536</v>
+        <v>50.99452580000001</v>
       </c>
       <c r="N90">
-        <v>53.9784464</v>
+        <v>53.4054742</v>
       </c>
       <c r="O90">
-        <v>12.954827136</v>
+        <v>12.817313808</v>
       </c>
       <c r="P90">
-        <v>41.023619264</v>
+        <v>40.588160392</v>
       </c>
       <c r="Q90">
-        <v>126.623619264</v>
+        <v>126.188160392</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7585356005222135</v>
+        <v>0.8209640368578305</v>
       </c>
       <c r="T90">
-        <v>3.501935274987523</v>
+        <v>3.808669417642709</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.070543102027701</v>
+        <v>2.047278572791435</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1415771640543613</v>
+        <v>0.1414350160460571</v>
       </c>
       <c r="C91">
-        <v>383.3301092461752</v>
+        <v>377.293261863907</v>
       </c>
       <c r="D91">
-        <v>1024.081109246175</v>
+        <v>1025.603261863907</v>
       </c>
       <c r="E91">
-        <v>345.051</v>
+        <v>352.61</v>
       </c>
       <c r="F91">
-        <v>672.751</v>
+        <v>680.3099999999999</v>
       </c>
       <c r="G91">
         <v>32</v>
@@ -8737,28 +8737,28 @@
         <v>104.4</v>
       </c>
       <c r="M91">
-        <v>50.99452580000001</v>
+        <v>51.567498</v>
       </c>
       <c r="N91">
-        <v>53.4054742</v>
+        <v>52.83250200000001</v>
       </c>
       <c r="O91">
-        <v>12.817313808</v>
+        <v>12.67980048</v>
       </c>
       <c r="P91">
-        <v>40.588160392</v>
+        <v>40.15270152000001</v>
       </c>
       <c r="Q91">
-        <v>126.188160392</v>
+        <v>125.75270152</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8209640368578305</v>
+        <v>0.8958781604605711</v>
       </c>
       <c r="T91">
-        <v>3.808669417642709</v>
+        <v>4.176750388828933</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.047278572791435</v>
+        <v>2.024531033093752</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1414350160460571</v>
+        <v>0.1412928680377528</v>
       </c>
       <c r="C92">
-        <v>377.293261863907</v>
+        <v>371.2609461491319</v>
       </c>
       <c r="D92">
-        <v>1025.603261863907</v>
+        <v>1027.129946149132</v>
       </c>
       <c r="E92">
-        <v>352.61</v>
+        <v>360.169</v>
       </c>
       <c r="F92">
-        <v>680.3099999999999</v>
+        <v>687.869</v>
       </c>
       <c r="G92">
         <v>32</v>
@@ -8819,28 +8819,28 @@
         <v>104.4</v>
       </c>
       <c r="M92">
-        <v>51.567498</v>
+        <v>52.14047020000001</v>
       </c>
       <c r="N92">
-        <v>52.83250200000001</v>
+        <v>52.2595298</v>
       </c>
       <c r="O92">
-        <v>12.67980048</v>
+        <v>12.542287152</v>
       </c>
       <c r="P92">
-        <v>40.15270152000001</v>
+        <v>39.717242648</v>
       </c>
       <c r="Q92">
-        <v>125.75270152</v>
+        <v>125.317242648</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8958781604605711</v>
+        <v>0.9874398670861428</v>
       </c>
       <c r="T92">
-        <v>4.176750388828933</v>
+        <v>4.626627131389872</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.024531033093752</v>
+        <v>2.002283439323491</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1412928680377528</v>
+        <v>0.1510793600294486</v>
       </c>
       <c r="C93">
-        <v>371.2609461491319</v>
+        <v>268.2226519208268</v>
       </c>
       <c r="D93">
-        <v>1027.129946149132</v>
+        <v>931.6506519208268</v>
       </c>
       <c r="E93">
-        <v>360.169</v>
+        <v>367.728</v>
       </c>
       <c r="F93">
-        <v>687.869</v>
+        <v>695.428</v>
       </c>
       <c r="G93">
         <v>32</v>
@@ -8901,45 +8901,45 @@
         <v>104.4</v>
       </c>
       <c r="M93">
-        <v>52.14047020000001</v>
+        <v>62.58852</v>
       </c>
       <c r="N93">
-        <v>52.2595298</v>
+        <v>41.81148000000001</v>
       </c>
       <c r="O93">
-        <v>12.542287152</v>
+        <v>10.0347552</v>
       </c>
       <c r="P93">
-        <v>39.717242648</v>
+        <v>31.77672480000001</v>
       </c>
       <c r="Q93">
-        <v>125.317242648</v>
+        <v>117.3767248</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9874398670861428</v>
+        <v>1.101892000368108</v>
       </c>
       <c r="T93">
-        <v>4.626627131389872</v>
+        <v>5.188973059591048</v>
       </c>
       <c r="U93">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V93">
         <v>0.24</v>
       </c>
       <c r="W93">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.002283439323491</v>
+        <v>1.668037525092461</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1510793600294486</v>
+        <v>0.1510451320211443</v>
       </c>
       <c r="C94">
-        <v>268.2226519208268</v>
+        <v>260.9666449964992</v>
       </c>
       <c r="D94">
-        <v>931.6506519208268</v>
+        <v>931.9536449964992</v>
       </c>
       <c r="E94">
-        <v>367.728</v>
+        <v>375.287</v>
       </c>
       <c r="F94">
-        <v>695.428</v>
+        <v>702.987</v>
       </c>
       <c r="G94">
         <v>32</v>
@@ -8983,28 +8983,28 @@
         <v>104.4</v>
       </c>
       <c r="M94">
-        <v>62.58852</v>
+        <v>63.26882999999999</v>
       </c>
       <c r="N94">
-        <v>41.81148000000001</v>
+        <v>41.13117000000001</v>
       </c>
       <c r="O94">
-        <v>10.0347552</v>
+        <v>9.871480800000002</v>
       </c>
       <c r="P94">
-        <v>31.77672480000001</v>
+        <v>31.25968920000001</v>
       </c>
       <c r="Q94">
-        <v>117.3767248</v>
+        <v>116.8596892</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.101892000368108</v>
+        <v>1.249044743159206</v>
       </c>
       <c r="T94">
-        <v>5.188973059591048</v>
+        <v>5.91198925299256</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.668037525092461</v>
+        <v>1.650101637725876</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1510451320211443</v>
+        <v>0.1510109040128401</v>
       </c>
       <c r="C95">
-        <v>260.9666449964992</v>
+        <v>253.7108352161766</v>
       </c>
       <c r="D95">
-        <v>931.9536449964992</v>
+        <v>932.2568352161767</v>
       </c>
       <c r="E95">
-        <v>375.287</v>
+        <v>382.8460000000001</v>
       </c>
       <c r="F95">
-        <v>702.987</v>
+        <v>710.546</v>
       </c>
       <c r="G95">
         <v>32</v>
@@ -9065,28 +9065,28 @@
         <v>104.4</v>
       </c>
       <c r="M95">
-        <v>63.26882999999999</v>
+        <v>63.94914</v>
       </c>
       <c r="N95">
-        <v>41.13117000000001</v>
+        <v>40.45086000000001</v>
       </c>
       <c r="O95">
-        <v>9.871480800000002</v>
+        <v>9.708206400000002</v>
       </c>
       <c r="P95">
-        <v>31.25968920000001</v>
+        <v>30.7426536</v>
       </c>
       <c r="Q95">
-        <v>116.8596892</v>
+        <v>116.3426536</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.249044743159206</v>
+        <v>1.445248400214003</v>
       </c>
       <c r="T95">
-        <v>5.91198925299256</v>
+        <v>6.876010844194575</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.650101637725876</v>
+        <v>1.632547364984111</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1510109040128401</v>
+        <v>0.1509766760045358</v>
       </c>
       <c r="C96">
-        <v>253.7108352161766</v>
+        <v>246.455222772331</v>
       </c>
       <c r="D96">
-        <v>932.2568352161767</v>
+        <v>932.560222772331</v>
       </c>
       <c r="E96">
-        <v>382.8460000000001</v>
+        <v>390.405</v>
       </c>
       <c r="F96">
-        <v>710.546</v>
+        <v>718.105</v>
       </c>
       <c r="G96">
         <v>32</v>
@@ -9147,28 +9147,28 @@
         <v>104.4</v>
       </c>
       <c r="M96">
-        <v>63.94914</v>
+        <v>64.62945000000001</v>
       </c>
       <c r="N96">
-        <v>40.45086000000001</v>
+        <v>39.77055</v>
       </c>
       <c r="O96">
-        <v>9.708206400000002</v>
+        <v>9.544931999999999</v>
       </c>
       <c r="P96">
-        <v>30.7426536</v>
+        <v>30.225618</v>
       </c>
       <c r="Q96">
-        <v>116.3426536</v>
+        <v>115.825618</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.445248400214003</v>
+        <v>1.719933520090719</v>
       </c>
       <c r="T96">
-        <v>6.876010844194575</v>
+        <v>8.225641071877398</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.632547364984111</v>
+        <v>1.615362655879015</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1509766760045358</v>
+        <v>0.1509424479962316</v>
       </c>
       <c r="C97">
-        <v>246.455222772331</v>
+        <v>239.1998078576852</v>
       </c>
       <c r="D97">
-        <v>932.560222772331</v>
+        <v>932.8638078576852</v>
       </c>
       <c r="E97">
-        <v>390.405</v>
+        <v>397.964</v>
       </c>
       <c r="F97">
-        <v>718.105</v>
+        <v>725.664</v>
       </c>
       <c r="G97">
         <v>32</v>
@@ -9229,28 +9229,28 @@
         <v>104.4</v>
       </c>
       <c r="M97">
-        <v>64.62945000000001</v>
+        <v>65.30976</v>
       </c>
       <c r="N97">
-        <v>39.77055</v>
+        <v>39.09024000000001</v>
       </c>
       <c r="O97">
-        <v>9.544931999999999</v>
+        <v>9.381657600000002</v>
       </c>
       <c r="P97">
-        <v>30.225618</v>
+        <v>29.7085824</v>
       </c>
       <c r="Q97">
-        <v>115.825618</v>
+        <v>115.3085824</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.719933520090719</v>
+        <v>2.131961199905793</v>
       </c>
       <c r="T97">
-        <v>8.225641071877398</v>
+        <v>10.25008641340163</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.615362655879015</v>
+        <v>1.598535961546942</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1509424479962316</v>
+        <v>0.1509082199879273</v>
       </c>
       <c r="C98">
-        <v>239.1998078576852</v>
+        <v>231.9445906652123</v>
       </c>
       <c r="D98">
-        <v>932.8638078576852</v>
+        <v>933.1675906652123</v>
       </c>
       <c r="E98">
-        <v>397.964</v>
+        <v>405.523</v>
       </c>
       <c r="F98">
-        <v>725.664</v>
+        <v>733.223</v>
       </c>
       <c r="G98">
         <v>32</v>
@@ -9311,28 +9311,28 @@
         <v>104.4</v>
       </c>
       <c r="M98">
-        <v>65.30976</v>
+        <v>65.99006999999999</v>
       </c>
       <c r="N98">
-        <v>39.09024000000001</v>
+        <v>38.40993000000002</v>
       </c>
       <c r="O98">
-        <v>9.381657600000002</v>
+        <v>9.218383200000003</v>
       </c>
       <c r="P98">
-        <v>29.7085824</v>
+        <v>29.19154680000001</v>
       </c>
       <c r="Q98">
-        <v>115.3085824</v>
+        <v>114.7915468</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.131961199905787</v>
+        <v>2.818673999597574</v>
       </c>
       <c r="T98">
-        <v>10.25008641340161</v>
+        <v>13.62416198260865</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.598535961546942</v>
+        <v>1.582056209366046</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1509082199879273</v>
+        <v>0.150873991979623</v>
       </c>
       <c r="C99">
-        <v>231.9445906652123</v>
+        <v>224.6895713881372</v>
       </c>
       <c r="D99">
-        <v>933.1675906652123</v>
+        <v>933.4715713881371</v>
       </c>
       <c r="E99">
-        <v>405.523</v>
+        <v>413.0819999999999</v>
       </c>
       <c r="F99">
-        <v>733.223</v>
+        <v>740.7819999999999</v>
       </c>
       <c r="G99">
         <v>32</v>
@@ -9393,28 +9393,28 @@
         <v>104.4</v>
       </c>
       <c r="M99">
-        <v>65.99006999999999</v>
+        <v>66.67037999999999</v>
       </c>
       <c r="N99">
-        <v>38.40993000000002</v>
+        <v>37.72962000000001</v>
       </c>
       <c r="O99">
-        <v>9.218383200000003</v>
+        <v>9.055108800000003</v>
       </c>
       <c r="P99">
-        <v>29.19154680000001</v>
+        <v>28.67451120000001</v>
       </c>
       <c r="Q99">
-        <v>114.7915468</v>
+        <v>114.2745112</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.818673999597574</v>
+        <v>4.192099598981149</v>
       </c>
       <c r="T99">
-        <v>13.62416198260865</v>
+        <v>20.37231312102273</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.582056209366046</v>
+        <v>1.565912778658229</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.150873991979623</v>
+        <v>0.1508397639713188</v>
       </c>
       <c r="C100">
-        <v>224.6895713881372</v>
+        <v>217.4347502199359</v>
       </c>
       <c r="D100">
-        <v>933.4715713881371</v>
+        <v>933.775750219936</v>
       </c>
       <c r="E100">
-        <v>413.0819999999999</v>
+        <v>420.641</v>
       </c>
       <c r="F100">
-        <v>740.7819999999999</v>
+        <v>748.341</v>
       </c>
       <c r="G100">
         <v>32</v>
@@ -9475,28 +9475,28 @@
         <v>104.4</v>
       </c>
       <c r="M100">
-        <v>66.67037999999999</v>
+        <v>67.35069</v>
       </c>
       <c r="N100">
-        <v>37.72962000000001</v>
+        <v>37.04931000000001</v>
       </c>
       <c r="O100">
-        <v>9.055108800000003</v>
+        <v>8.8918344</v>
       </c>
       <c r="P100">
-        <v>28.67451120000001</v>
+        <v>28.15747560000001</v>
       </c>
       <c r="Q100">
-        <v>114.2745112</v>
+        <v>113.7574756</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.192099598981149</v>
+        <v>8.312376397131873</v>
       </c>
       <c r="T100">
-        <v>20.37231312102273</v>
+        <v>40.61676653626499</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.565912778658229</v>
+        <v>1.550095477863701</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1508397639713188</v>
-      </c>
-      <c r="C101">
-        <v>217.4347502199359</v>
-      </c>
-      <c r="D101">
-        <v>933.775750219936</v>
-      </c>
-      <c r="E101">
-        <v>420.641</v>
-      </c>
-      <c r="F101">
-        <v>748.341</v>
-      </c>
-      <c r="G101">
-        <v>32</v>
-      </c>
-      <c r="H101">
-        <v>428.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>190</v>
-      </c>
-      <c r="K101">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="L101">
-        <v>104.4</v>
-      </c>
-      <c r="M101">
-        <v>67.35069</v>
-      </c>
-      <c r="N101">
-        <v>37.04931000000001</v>
-      </c>
-      <c r="O101">
-        <v>8.8918344</v>
-      </c>
-      <c r="P101">
-        <v>28.15747560000001</v>
-      </c>
-      <c r="Q101">
-        <v>113.7574756</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.312376397131873</v>
-      </c>
-      <c r="T101">
-        <v>40.61676653626499</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.24</v>
-      </c>
-      <c r="W101">
-        <v>0.0684</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.550095477863701</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
